--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>260174000000</v>
+        <v>365817000000</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>274515000000</v>
+        <v>394328000000</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>365817000000</v>
+        <v>383285000000</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>394328000000</v>
+        <v>391035000000</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>383285000000</v>
+        <v>416161000000</v>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>98392000000</v>
+        <v>152836000000</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>104956000000</v>
+        <v>170782000000</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>152836000000</v>
+        <v>169148000000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>170782000000</v>
+        <v>180683000000</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>169148000000</v>
+        <v>195201000000</v>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>63930000000</v>
+        <v>108949000000</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>66288000000</v>
+        <v>119437000000</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>108949000000</v>
+        <v>114301000000</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>119437000000</v>
+        <v>123216000000</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>114301000000</v>
+        <v>133050000000</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -825,19 +825,19 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>55256000000</v>
+        <v>94680000000</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>57411000000</v>
+        <v>99803000000</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>94680000000</v>
+        <v>96995000000</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>99803000000</v>
+        <v>93736000000</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>96995000000</v>
+        <v>112010000000</v>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>2.97</v>
+        <v>5.61</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>3.28</v>
+        <v>6.11</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>5.61</v>
+        <v>6.13</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>6.11</v>
+        <v>6.08</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>6.13</v>
+        <v>7.46</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -918,19 +918,19 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>18595651000</v>
+        <v>16864919000</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>17528214000</v>
+        <v>16325819000</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>16864919000</v>
+        <v>15812547000</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>16325819000</v>
+        <v>15408095000</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>15812547000</v>
+        <v>15004697000</v>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>69391000000</v>
+        <v>104038000000</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>80674000000</v>
+        <v>122151000000</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>104038000000</v>
+        <v>110543000000</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>122151000000</v>
+        <v>118254000000</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>110543000000</v>
+        <v>111482000000</v>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>10495000000</v>
+        <v>11085000000</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>7309000000</v>
+        <v>10708000000</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>11085000000</v>
+        <v>10959000000</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>10708000000</v>
+        <v>9447000000</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>10959000000</v>
+        <v>12715000000</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>38016000000</v>
+        <v>34940000000</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>34940000000</v>
+        <v>23646000000</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>23646000000</v>
+        <v>29965000000</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>29965000000</v>
+        <v>29943000000</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>29943000000</v>
+        <v>35934000000</v>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
@@ -1136,19 +1136,19 @@
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>107440000000</v>
+        <v>118719000000</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>118719000000</v>
+        <v>110087000000</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>110087000000</v>
+        <v>105103000000</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>105103000000</v>
+        <v>96662000000</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>96662000000</v>
+        <v>90678000000</v>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
@@ -1163,19 +1163,19 @@
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>69424000000</v>
+        <v>83779000000</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>83779000000</v>
+        <v>86441000000</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>86441000000</v>
+        <v>75138000000</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>75138000000</v>
+        <v>66719000000</v>
       </c>
       <c r="H31" s="20" t="n">
-        <v>66719000000</v>
+        <v>54744000000</v>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
@@ -1190,19 +1190,19 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>107147000000</v>
+        <v>63090000000</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>90488000000</v>
+        <v>50672000000</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>65339000000</v>
+        <v>62146000000</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>63090000000</v>
+        <v>56950000000</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>50672000000</v>
+        <v>73733000000</v>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
@@ -1330,19 +1330,19 @@
         </is>
       </c>
       <c r="D7" s="20" t="n">
-        <v>260174000000</v>
+        <v>365817000000</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>274515000000</v>
+        <v>394328000000</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>365817000000</v>
+        <v>383285000000</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>394328000000</v>
+        <v>391035000000</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>383285000000</v>
+        <v>416161000000</v>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
@@ -1385,19 +1385,19 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>161782000000</v>
+        <v>212981000000</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>169559000000</v>
+        <v>223546000000</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>212981000000</v>
+        <v>214137000000</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>223546000000</v>
+        <v>210352000000</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>214137000000</v>
+        <v>220960000000</v>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="D10" s="20" t="n">
-        <v>98392000000</v>
+        <v>152836000000</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>104956000000</v>
+        <v>170782000000</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>152836000000</v>
+        <v>169148000000</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>170782000000</v>
+        <v>180683000000</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>169148000000</v>
+        <v>195201000000</v>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>16217000000</v>
+        <v>21914000000</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>18752000000</v>
+        <v>26251000000</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>21914000000</v>
+        <v>29915000000</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>26251000000</v>
+        <v>31370000000</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>29915000000</v>
+        <v>34550000000</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>18245000000</v>
+        <v>21973000000</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>19916000000</v>
+        <v>25094000000</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>21973000000</v>
+        <v>24932000000</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>25094000000</v>
+        <v>26097000000</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>24932000000</v>
+        <v>27601000000</v>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="D14" s="20" t="n">
-        <v>63930000000</v>
+        <v>108949000000</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>66288000000</v>
+        <v>119437000000</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>108949000000</v>
+        <v>114301000000</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>119437000000</v>
+        <v>123216000000</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>114301000000</v>
+        <v>133050000000</v>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3576000000</v>
+        <v>2645000000</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>2873000000</v>
+        <v>2931000000</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>2645000000</v>
+        <v>3933000000</v>
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
@@ -1605,19 +1605,19 @@
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>65737000000</v>
+        <v>109207000000</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>67091000000</v>
+        <v>119103000000</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>109207000000</v>
+        <v>113736000000</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>119103000000</v>
+        <v>123485000000</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>113736000000</v>
+        <v>132729000000</v>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
@@ -1632,19 +1632,19 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>10481000000</v>
+        <v>14527000000</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>9680000000</v>
+        <v>19300000000</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>14527000000</v>
+        <v>16741000000</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>19300000000</v>
+        <v>29749000000</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>16741000000</v>
+        <v>20719000000</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1659,19 +1659,19 @@
         </is>
       </c>
       <c r="D19" s="20" t="n">
-        <v>55256000000</v>
+        <v>94680000000</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>57411000000</v>
+        <v>99803000000</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>94680000000</v>
+        <v>96995000000</v>
       </c>
       <c r="G19" s="20" t="n">
-        <v>99803000000</v>
+        <v>93736000000</v>
       </c>
       <c r="H19" s="20" t="n">
-        <v>96995000000</v>
+        <v>112010000000</v>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
@@ -1805,19 +1805,19 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>38016000000</v>
+        <v>34940000000</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>34940000000</v>
+        <v>23646000000</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>23646000000</v>
+        <v>29965000000</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>29965000000</v>
+        <v>29943000000</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>29943000000</v>
+        <v>35934000000</v>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>16120000000</v>
+        <v>26278000000</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>26278000000</v>
+        <v>28184000000</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>28184000000</v>
+        <v>29508000000</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>29508000000</v>
+        <v>33410000000</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>33410000000</v>
+        <v>39777000000</v>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>4061000000</v>
+        <v>6580000000</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6580000000</v>
+        <v>4946000000</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4946000000</v>
+        <v>6331000000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>6331000000</v>
+        <v>7286000000</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7286000000</v>
+        <v>5718000000</v>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="D11" s="20" t="n">
-        <v>143713000000</v>
+        <v>134836000000</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>134836000000</v>
+        <v>135405000000</v>
       </c>
       <c r="F11" s="20" t="n">
-        <v>135405000000</v>
+        <v>143566000000</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>143566000000</v>
+        <v>152987000000</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>152987000000</v>
+        <v>147957000000</v>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
@@ -1945,19 +1945,19 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>36766000000</v>
+        <v>39440000000</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>39440000000</v>
+        <v>42117000000</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>42117000000</v>
+        <v>43715000000</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>43715000000</v>
+        <v>45680000000</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>45680000000</v>
+        <v>49834000000</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -2004,19 +2004,19 @@
         </is>
       </c>
       <c r="D14" s="20" t="n">
-        <v>323888000000</v>
+        <v>351002000000</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>351002000000</v>
+        <v>352755000000</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>352755000000</v>
+        <v>352583000000</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>352583000000</v>
+        <v>364980000000</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>364980000000</v>
+        <v>359241000000</v>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
@@ -2031,19 +2031,19 @@
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>42296000000</v>
+        <v>54763000000</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>54763000000</v>
+        <v>64115000000</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>64115000000</v>
+        <v>62611000000</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>62611000000</v>
+        <v>68960000000</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>68960000000</v>
+        <v>69860000000</v>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
@@ -2058,19 +2058,19 @@
         </is>
       </c>
       <c r="D16" s="20" t="n">
-        <v>105392000000</v>
+        <v>125481000000</v>
       </c>
       <c r="E16" s="20" t="n">
-        <v>125481000000</v>
+        <v>153982000000</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>153982000000</v>
+        <v>145308000000</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>145308000000</v>
+        <v>176392000000</v>
       </c>
       <c r="H16" s="20" t="n">
-        <v>176392000000</v>
+        <v>165631000000</v>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
@@ -2085,19 +2085,19 @@
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>8773000000</v>
+        <v>9613000000</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>9613000000</v>
+        <v>11128000000</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>11128000000</v>
+        <v>9822000000</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>9822000000</v>
+        <v>10912000000</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>10912000000</v>
+        <v>12350000000</v>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
@@ -2112,19 +2112,19 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>98667000000</v>
+        <v>109106000000</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>109106000000</v>
+        <v>98959000000</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>98959000000</v>
+        <v>95281000000</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>95281000000</v>
+        <v>85750000000</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>85750000000</v>
+        <v>78328000000</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="D19" s="20" t="n">
-        <v>258549000000</v>
+        <v>287912000000</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>287912000000</v>
+        <v>302083000000</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>302083000000</v>
+        <v>290437000000</v>
       </c>
       <c r="G19" s="20" t="n">
-        <v>290437000000</v>
+        <v>308030000000</v>
       </c>
       <c r="H19" s="20" t="n">
-        <v>308030000000</v>
+        <v>285508000000</v>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="D20" s="20" t="n">
-        <v>107147000000</v>
+        <v>63090000000</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>90488000000</v>
+        <v>50672000000</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>65339000000</v>
+        <v>62146000000</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>63090000000</v>
+        <v>56950000000</v>
       </c>
       <c r="H20" s="20" t="n">
-        <v>50672000000</v>
+        <v>73733000000</v>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
@@ -2193,19 +2193,19 @@
         </is>
       </c>
       <c r="D22" s="20" t="n">
-        <v>323888000000</v>
+        <v>351002000000</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>351002000000</v>
+        <v>352755000000</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>352755000000</v>
+        <v>352583000000</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>352583000000</v>
+        <v>364980000000</v>
       </c>
       <c r="H22" s="20" t="n">
-        <v>364980000000</v>
+        <v>359241000000</v>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
@@ -2351,19 +2351,19 @@
         </is>
       </c>
       <c r="D7" s="20" t="n">
-        <v>69391000000</v>
+        <v>104038000000</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>80674000000</v>
+        <v>122151000000</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>104038000000</v>
+        <v>110543000000</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>122151000000</v>
+        <v>118254000000</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>110543000000</v>
+        <v>111482000000</v>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
@@ -2378,19 +2378,19 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>10495000000</v>
+        <v>11085000000</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7309000000</v>
+        <v>10708000000</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>11085000000</v>
+        <v>10959000000</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>10708000000</v>
+        <v>9447000000</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>10959000000</v>
+        <v>12715000000</v>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
@@ -2405,19 +2405,19 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>45896000000</v>
+        <v>-14545000000</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>-4289000000</v>
+        <v>-22354000000</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>-14545000000</v>
+        <v>3705000000</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>-22354000000</v>
+        <v>2935000000</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>3705000000</v>
+        <v>15195000000</v>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>-90976000000</v>
+        <v>-93353000000</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>-86820000000</v>
+        <v>-110749000000</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>-93353000000</v>
+        <v>-108488000000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>-110749000000</v>
+        <v>-121983000000</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>-108488000000</v>
+        <v>-120686000000</v>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
@@ -2459,19 +2459,19 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>66897000000</v>
+        <v>85971000000</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>72358000000</v>
+        <v>89402000000</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>85971000000</v>
+        <v>77550000000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>89402000000</v>
+        <v>94949000000</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>77550000000</v>
+        <v>90711000000</v>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:GrossProfit · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:GrossProfit · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:GrossProfit · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:GrossProfit · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:GrossProfit · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:GrossProfit · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:GrossProfit · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:GrossProfit · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:GrossProfit · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:GrossProfit · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:OperatingIncomeLoss · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:OperatingIncomeLoss · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:OperatingIncomeLoss · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:OperatingIncomeLoss · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:OperatingIncomeLoss · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:OperatingIncomeLoss · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E22" s="25" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D23" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:NetIncomeLoss · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E23" s="25" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:NetIncomeLoss · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:NetIncomeLoss · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:NetIncomeLoss · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E26" s="25" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetIncomeLoss · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:NetIncomeLoss · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E27" s="25" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:EarningsPerShareDiluted · period ending 2019-09-28 · USD/shares · filed 2021-10-29</t>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2021-09-25 · USD/shares · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E28" s="25" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D29" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:EarningsPerShareDiluted · period ending 2020-09-26 · USD/shares · filed 2022-10-28</t>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2022-09-24 · USD/shares · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E29" s="25" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="D30" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:EarningsPerShareDiluted · period ending 2021-09-25 · USD/shares · filed 2023-11-03</t>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2023-09-30 · USD/shares · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E30" s="25" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:EarningsPerShareDiluted · period ending 2022-09-24 · USD/shares · filed 2024-11-01</t>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2024-09-28 · USD/shares · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E31" s="25" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="D32" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:EarningsPerShareDiluted · period ending 2023-09-30 · USD/shares · filed 2025-10-31</t>
+          <t>us-gaap:EarningsPerShareDiluted · period ending 2025-09-27 · USD/shares · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E32" s="25" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D33" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2019-09-28 · shares · filed 2021-10-29</t>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2021-09-25 · shares · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2020-09-26 · shares · filed 2022-10-28</t>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2022-09-24 · shares · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="D35" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2021-09-25 · shares · filed 2023-11-03</t>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2023-09-30 · shares · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2022-09-24 · shares · filed 2024-11-01</t>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2024-09-28 · shares · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E36" s="25" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D37" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2023-09-30 · shares · filed 2025-10-31</t>
+          <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-09-27 · shares · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E38" s="25" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E39" s="25" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E40" s="25" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E41" s="25" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E42" s="25" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E43" s="25" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D44" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E44" s="25" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D45" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E45" s="25" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E46" s="25" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D47" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E47" s="25" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E48" s="25" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E49" s="25" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E50" s="25" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E51" s="25" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D52" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E52" s="25" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D53" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:LongTermDebtNoncurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E53" s="25" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:LongTermDebtNoncurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E54" s="25" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:LongTermDebtNoncurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E55" s="25" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:LongTermDebtNoncurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E56" s="25" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:LongTermDebtNoncurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E57" s="25" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E58" s="25" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E59" s="25" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E60" s="25" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E61" s="25" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E62" s="25" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2018-09-29 · USD · filed 2021-10-29</t>
+          <t>us-gaap:StockholdersEquity · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E63" s="25" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2019-09-28 · USD · filed 2022-10-28</t>
+          <t>us-gaap:StockholdersEquity · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E64" s="25" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2020-09-26 · USD · filed 2023-11-03</t>
+          <t>us-gaap:StockholdersEquity · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E65" s="25" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2021-09-25 · USD · filed 2024-11-01</t>
+          <t>us-gaap:StockholdersEquity · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E66" s="25" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2022-09-24 · USD · filed 2025-10-31</t>
+          <t>us-gaap:StockholdersEquity · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E67" s="25" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E68" s="25" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E69" s="25" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E70" s="25" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E71" s="25" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E72" s="25" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E73" s="25" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E74" s="25" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E75" s="25" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E76" s="25" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E77" s="25" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E78" s="25" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E79" s="25" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E80" s="25" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E81" s="25" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E82" s="25" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InterestExpense · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:InterestExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E83" s="25" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InterestExpense · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:InterestExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E84" s="25" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InterestExpense · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:InterestExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E85" s="25" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E86" s="25" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E87" s="25" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E88" s="25" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E89" s="25" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E90" s="25" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E91" s="25" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E92" s="25" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E93" s="25" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E94" s="25" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E95" s="25" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E96" s="25" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E97" s="25" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E98" s="25" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E99" s="25" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E100" s="25" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:InventoryNet · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E101" s="25" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:InventoryNet · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E102" s="25" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:InventoryNet · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E103" s="25" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:InventoryNet · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E104" s="25" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:InventoryNet · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E105" s="25" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:AssetsCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E106" s="25" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:AssetsCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E107" s="25" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:AssetsCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E108" s="25" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:AssetsCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E109" s="25" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:AssetsCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E110" s="25" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E111" s="25" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E112" s="25" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E113" s="25" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E114" s="25" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E115" s="25" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:Assets · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E116" s="25" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:Assets · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E117" s="25" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:Assets · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E118" s="25" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:Assets · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E119" s="25" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:Assets · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E120" s="25" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E121" s="25" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E122" s="25" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E123" s="25" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E124" s="25" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E125" s="25" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E126" s="25" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E127" s="25" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E128" s="25" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E129" s="25" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E130" s="25" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:Liabilities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E131" s="25" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:Liabilities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E132" s="25" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:Liabilities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E133" s="25" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:Liabilities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E134" s="25" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:Liabilities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E135" s="25" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2020-09-26 · USD · filed 2021-10-29</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E136" s="25" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2021-09-25 · USD · filed 2022-10-28</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2022-09-24 · USD · filed 2023-11-03</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E138" s="25" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2023-09-30 · USD · filed 2024-11-01</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E139" s="25" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2024-09-28 · USD · filed 2025-10-31</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E140" s="25" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E141" s="25" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E142" s="25" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E143" s="25" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E144" s="25" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E145" s="25" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E146" s="25" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E147" s="25" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E148" s="25" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E149" s="25" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E150" s="25" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2019-09-28 · USD · filed 2021-10-29</t>
+          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E151" s="25" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2020-09-26 · USD · filed 2022-10-28</t>
+          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E152" s="25" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2021-09-25 · USD · filed 2023-11-03</t>
+          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E153" s="25" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2022-09-24 · USD · filed 2024-11-01</t>
+          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E154" s="25" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2023-09-30 · USD · filed 2025-10-31</t>
+          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E155" s="25" t="inlineStr">

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -175,11 +175,11 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1103,29 +1103,24 @@
           <t>Short-term investments</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D29" s="10" t="n">
+        <v>27699000000</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>24658000000</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>31590000000</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>35228000000</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>18763000000</v>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>[46][47][48][49][50]</t>
         </is>
       </c>
     </row>
@@ -1136,23 +1131,23 @@
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>118719000000</v>
+        <v>127676000000</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>110087000000</v>
+        <v>122952000000</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>105103000000</v>
+        <v>116394000000</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>96662000000</v>
+        <v>108253000000</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>90678000000</v>
+        <v>103631000000</v>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>[46][47][48][49][50]</t>
+          <t>[51][52][53][54][55]</t>
         </is>
       </c>
     </row>
@@ -1162,24 +1157,24 @@
           <t>Net debt / (net cash)</t>
         </is>
       </c>
-      <c r="D31" s="20" t="n">
-        <v>83779000000</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>86441000000</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>75138000000</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>66719000000</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <v>54744000000</v>
+      <c r="D31" s="19" t="n">
+        <v>65037000000</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>74648000000</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>54839000000</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>43082000000</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>48934000000</v>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>[51][52][53][54][55]</t>
+          <t>[56][57][58][59][60]</t>
         </is>
       </c>
     </row>
@@ -1206,26 +1201,26 @@
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>[56][57][58][59][60]</t>
+          <t>[61][62][63][64][65]</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Blue = value as tagged in the filing. Black = formula computed in this workbook.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>An em dash means the filer did not tag that line. It does not mean zero.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>Not tagged by this filer: minority_interest</t>
         </is>
@@ -1329,19 +1324,19 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="19" t="n">
         <v>365817000000</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="19" t="n">
         <v>394328000000</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>383285000000</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="19" t="n">
         <v>391035000000</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>416161000000</v>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -1401,7 +1396,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>[61][62][63][64][65]</t>
+          <t>[66][67][68][69][70]</t>
         </is>
       </c>
     </row>
@@ -1411,19 +1406,19 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="19" t="n">
         <v>152836000000</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="19" t="n">
         <v>170782000000</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <v>169148000000</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="19" t="n">
         <v>180683000000</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="19" t="n">
         <v>195201000000</v>
       </c>
       <c r="J10" s="11" t="inlineStr">
@@ -1482,7 +1477,7 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>[66][67][68][69][70]</t>
+          <t>[71][72][73][74][75]</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1504,7 @@
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>[71][72][73][74][75]</t>
+          <t>[76][77][78][79][80]</t>
         </is>
       </c>
     </row>
@@ -1519,19 +1514,19 @@
           <t>Operating income</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="19" t="n">
         <v>108949000000</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="19" t="n">
         <v>119437000000</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="19" t="n">
         <v>114301000000</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="19" t="n">
         <v>123216000000</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="19" t="n">
         <v>133050000000</v>
       </c>
       <c r="J14" s="11" t="inlineStr">
@@ -1582,19 +1577,19 @@
       <c r="F16" s="10" t="n">
         <v>3933000000</v>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>[76][77][78]</t>
+          <t>[81][82][83]</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1616,7 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>[79][80][81][82][83]</t>
+          <t>[84][85][86][87][88]</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1643,7 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>[84][85][86][87][88]</t>
+          <t>[89][90][91][92][93]</t>
         </is>
       </c>
     </row>
@@ -1658,19 +1653,19 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="19" t="n">
         <v>94680000000</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E19" s="19" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F19" s="20" t="n">
+      <c r="F19" s="19" t="n">
         <v>96995000000</v>
       </c>
-      <c r="G19" s="20" t="n">
+      <c r="G19" s="19" t="n">
         <v>93736000000</v>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="19" t="n">
         <v>112010000000</v>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -1831,29 +1826,24 @@
           <t>Short-term investments</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D8" s="10" t="n">
+        <v>27699000000</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>24658000000</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>31590000000</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>35228000000</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>18763000000</v>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>[46][47][48][49][50]</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1870,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>[89][90][91][92][93]</t>
+          <t>[94][95][96][97][98]</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1897,7 @@
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>[94][95][96][97][98]</t>
+          <t>[99][100][101][102][103]</t>
         </is>
       </c>
     </row>
@@ -1917,24 +1907,24 @@
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="19" t="n">
         <v>134836000000</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="19" t="n">
         <v>135405000000</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>143566000000</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>152987000000</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="19" t="n">
         <v>147957000000</v>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>[99][100][101][102][103]</t>
+          <t>[104][105][106][107][108]</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1951,7 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>[104][105][106][107][108]</t>
+          <t>[109][110][111][112][113]</t>
         </is>
       </c>
     </row>
@@ -1971,27 +1961,27 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2003,24 +1993,24 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="19" t="n">
         <v>351002000000</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="19" t="n">
         <v>352755000000</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="19" t="n">
         <v>352583000000</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="19" t="n">
         <v>364980000000</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="19" t="n">
         <v>359241000000</v>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>[109][110][111][112][113]</t>
+          <t>[114][115][116][117][118]</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2037,7 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>[114][115][116][117][118]</t>
+          <t>[119][120][121][122][123]</t>
         </is>
       </c>
     </row>
@@ -2057,24 +2047,24 @@
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="19" t="n">
         <v>125481000000</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="19" t="n">
         <v>153982000000</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="19" t="n">
         <v>145308000000</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="19" t="n">
         <v>176392000000</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" s="19" t="n">
         <v>165631000000</v>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>[119][120][121][122][123]</t>
+          <t>[124][125][126][127][128]</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2091,7 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>[51][52][53][54][55]</t>
+          <t>[56][57][58][59][60]</t>
         </is>
       </c>
     </row>
@@ -2112,23 +2102,23 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>109106000000</v>
+        <v>118063000000</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>98959000000</v>
+        <v>111824000000</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>95281000000</v>
+        <v>106572000000</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>85750000000</v>
+        <v>97341000000</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>78328000000</v>
+        <v>91281000000</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>[46][47][48][49][50]</t>
+          <t>[51][52][53][54][55]</t>
         </is>
       </c>
     </row>
@@ -2138,24 +2128,24 @@
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="19" t="n">
         <v>287912000000</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E19" s="19" t="n">
         <v>302083000000</v>
       </c>
-      <c r="F19" s="20" t="n">
+      <c r="F19" s="19" t="n">
         <v>290437000000</v>
       </c>
-      <c r="G19" s="20" t="n">
+      <c r="G19" s="19" t="n">
         <v>308030000000</v>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="19" t="n">
         <v>285508000000</v>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>[124][125][126][127][128]</t>
+          <t>[129][130][131][132][133]</t>
         </is>
       </c>
     </row>
@@ -2165,24 +2155,24 @@
           <t>Total shareholders' equity</t>
         </is>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D20" s="19" t="n">
         <v>63090000000</v>
       </c>
-      <c r="E20" s="20" t="n">
+      <c r="E20" s="19" t="n">
         <v>50672000000</v>
       </c>
-      <c r="F20" s="20" t="n">
+      <c r="F20" s="19" t="n">
         <v>62146000000</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="19" t="n">
         <v>56950000000</v>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H20" s="19" t="n">
         <v>73733000000</v>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>[56][57][58][59][60]</t>
+          <t>[61][62][63][64][65]</t>
         </is>
       </c>
     </row>
@@ -2192,24 +2182,24 @@
           <t>Total liabilities and equity</t>
         </is>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D22" s="19" t="n">
         <v>351002000000</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="19" t="n">
         <v>352755000000</v>
       </c>
-      <c r="F22" s="20" t="n">
+      <c r="F22" s="19" t="n">
         <v>352583000000</v>
       </c>
-      <c r="G22" s="20" t="n">
+      <c r="G22" s="19" t="n">
         <v>364980000000</v>
       </c>
-      <c r="H22" s="20" t="n">
+      <c r="H22" s="19" t="n">
         <v>359241000000</v>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>[129][130][131][132][133]</t>
+          <t>[134][135][136][137][138]</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2231,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A non-zero balance check is highlighted red. It means the filer's tagged totals do not tie, and the workbook should not be used until the discrepancy is understood.</t>
         </is>
@@ -2350,19 +2340,19 @@
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="19" t="n">
         <v>104038000000</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="19" t="n">
         <v>122151000000</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>110543000000</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="19" t="n">
         <v>118254000000</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>111482000000</v>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -2421,7 +2411,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>[134][135][136][137][138]</t>
+          <t>[139][140][141][142][143]</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2438,7 @@
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>[139][140][141][142][143]</t>
+          <t>[144][145][146][147][148]</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2465,7 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>[144][145][146][147][148]</t>
+          <t>[149][150][151][152][153]</t>
         </is>
       </c>
     </row>
@@ -2485,29 +2475,24 @@
           <t>Dividends paid</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D12" s="10" t="n">
+        <v>14467000000</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>14841000000</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>15025000000</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>15234000000</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>15421000000</v>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>[154][155][156][157][158]</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F155"/>
+  <dimension ref="B2:F165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3946,7 +3931,7 @@
       </c>
       <c r="D53" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:MarketableSecuritiesCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E53" s="25" t="inlineStr">
@@ -3971,7 +3956,7 @@
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:MarketableSecuritiesCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E54" s="25" t="inlineStr">
@@ -3996,7 +3981,7 @@
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:MarketableSecuritiesCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E55" s="25" t="inlineStr">
@@ -4021,7 +4006,7 @@
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:MarketableSecuritiesCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E56" s="25" t="inlineStr">
@@ -4046,7 +4031,7 @@
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtNoncurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:MarketableSecuritiesCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E57" s="25" t="inlineStr">
@@ -4071,7 +4056,7 @@
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E58" s="25" t="inlineStr">
@@ -4096,7 +4081,7 @@
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E59" s="25" t="inlineStr">
@@ -4121,7 +4106,7 @@
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E60" s="25" t="inlineStr">
@@ -4146,7 +4131,7 @@
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E61" s="25" t="inlineStr">
@@ -4171,7 +4156,7 @@
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LongTermDebtCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E62" s="25" t="inlineStr">
@@ -4196,7 +4181,7 @@
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E63" s="25" t="inlineStr">
@@ -4221,7 +4206,7 @@
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E64" s="25" t="inlineStr">
@@ -4246,7 +4231,7 @@
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E65" s="25" t="inlineStr">
@@ -4271,7 +4256,7 @@
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E66" s="25" t="inlineStr">
@@ -4296,7 +4281,7 @@
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:StockholdersEquity · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:LongTermDebtCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E67" s="25" t="inlineStr">
@@ -4321,7 +4306,7 @@
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:StockholdersEquity · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E68" s="25" t="inlineStr">
@@ -4346,7 +4331,7 @@
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:StockholdersEquity · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E69" s="25" t="inlineStr">
@@ -4371,7 +4356,7 @@
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:StockholdersEquity · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E70" s="25" t="inlineStr">
@@ -4396,7 +4381,7 @@
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:StockholdersEquity · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E71" s="25" t="inlineStr">
@@ -4421,7 +4406,7 @@
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:StockholdersEquity · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E72" s="25" t="inlineStr">
@@ -4446,7 +4431,7 @@
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E73" s="25" t="inlineStr">
@@ -4471,7 +4456,7 @@
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E74" s="25" t="inlineStr">
@@ -4496,7 +4481,7 @@
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E75" s="25" t="inlineStr">
@@ -4521,7 +4506,7 @@
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E76" s="25" t="inlineStr">
@@ -4546,7 +4531,7 @@
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E77" s="25" t="inlineStr">
@@ -4571,7 +4556,7 @@
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E78" s="25" t="inlineStr">
@@ -4596,7 +4581,7 @@
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E79" s="25" t="inlineStr">
@@ -4621,7 +4606,7 @@
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E80" s="25" t="inlineStr">
@@ -4646,7 +4631,7 @@
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E81" s="25" t="inlineStr">
@@ -4671,7 +4656,7 @@
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E82" s="25" t="inlineStr">
@@ -4696,7 +4681,7 @@
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InterestExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E83" s="25" t="inlineStr">
@@ -4721,7 +4706,7 @@
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InterestExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E84" s="25" t="inlineStr">
@@ -4746,7 +4731,7 @@
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InterestExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E85" s="25" t="inlineStr">
@@ -4766,22 +4751,22 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>AAPL FY2021 10-K</t>
+          <t>AAPL FY2024 10-K</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E86" s="25" t="inlineStr">
         <is>
-          <t>0000320193-21-000105</t>
+          <t>0000320193-24-000123</t>
         </is>
       </c>
       <c r="F86" s="26" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
@@ -4791,22 +4776,22 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>AAPL FY2022 10-K</t>
+          <t>AAPL FY2025 10-K</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E87" s="25" t="inlineStr">
         <is>
-          <t>0000320193-22-000108</t>
+          <t>0000320193-25-000079</t>
         </is>
       </c>
       <c r="F87" s="26" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
@@ -4816,22 +4801,22 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>AAPL FY2023 10-K</t>
+          <t>AAPL FY2021 10-K</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:InterestExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E88" s="25" t="inlineStr">
         <is>
-          <t>0000320193-23-000106</t>
+          <t>0000320193-21-000105</t>
         </is>
       </c>
       <c r="F88" s="26" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
@@ -4841,22 +4826,22 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>AAPL FY2024 10-K</t>
+          <t>AAPL FY2022 10-K</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:InterestExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E89" s="25" t="inlineStr">
         <is>
-          <t>0000320193-24-000123</t>
+          <t>0000320193-22-000108</t>
         </is>
       </c>
       <c r="F89" s="26" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
@@ -4866,22 +4851,22 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>AAPL FY2025 10-K</t>
+          <t>AAPL FY2023 10-K</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:InterestExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E90" s="25" t="inlineStr">
         <is>
-          <t>0000320193-25-000079</t>
+          <t>0000320193-23-000106</t>
         </is>
       </c>
       <c r="F90" s="26" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4881,7 @@
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E91" s="25" t="inlineStr">
@@ -4921,7 +4906,7 @@
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E92" s="25" t="inlineStr">
@@ -4946,7 +4931,7 @@
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E93" s="25" t="inlineStr">
@@ -4971,7 +4956,7 @@
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E94" s="25" t="inlineStr">
@@ -4996,7 +4981,7 @@
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E95" s="25" t="inlineStr">
@@ -5021,7 +5006,7 @@
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E96" s="25" t="inlineStr">
@@ -5046,7 +5031,7 @@
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E97" s="25" t="inlineStr">
@@ -5071,7 +5056,7 @@
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E98" s="25" t="inlineStr">
@@ -5096,7 +5081,7 @@
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E99" s="25" t="inlineStr">
@@ -5121,7 +5106,7 @@
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E100" s="25" t="inlineStr">
@@ -5146,7 +5131,7 @@
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E101" s="25" t="inlineStr">
@@ -5171,7 +5156,7 @@
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E102" s="25" t="inlineStr">
@@ -5196,7 +5181,7 @@
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E103" s="25" t="inlineStr">
@@ -5221,7 +5206,7 @@
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E104" s="25" t="inlineStr">
@@ -5246,7 +5231,7 @@
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:InventoryNet · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:AccountsReceivableNetCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E105" s="25" t="inlineStr">
@@ -5271,7 +5256,7 @@
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:InventoryNet · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E106" s="25" t="inlineStr">
@@ -5296,7 +5281,7 @@
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:InventoryNet · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E107" s="25" t="inlineStr">
@@ -5321,7 +5306,7 @@
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:InventoryNet · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E108" s="25" t="inlineStr">
@@ -5346,7 +5331,7 @@
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:InventoryNet · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E109" s="25" t="inlineStr">
@@ -5371,7 +5356,7 @@
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AssetsCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:InventoryNet · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E110" s="25" t="inlineStr">
@@ -5396,7 +5381,7 @@
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:AssetsCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E111" s="25" t="inlineStr">
@@ -5421,7 +5406,7 @@
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:AssetsCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E112" s="25" t="inlineStr">
@@ -5446,7 +5431,7 @@
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:AssetsCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E113" s="25" t="inlineStr">
@@ -5471,7 +5456,7 @@
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:AssetsCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E114" s="25" t="inlineStr">
@@ -5496,7 +5481,7 @@
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:AssetsCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E115" s="25" t="inlineStr">
@@ -5521,7 +5506,7 @@
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E116" s="25" t="inlineStr">
@@ -5546,7 +5531,7 @@
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E117" s="25" t="inlineStr">
@@ -5571,7 +5556,7 @@
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E118" s="25" t="inlineStr">
@@ -5596,7 +5581,7 @@
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E119" s="25" t="inlineStr">
@@ -5621,7 +5606,7 @@
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Assets · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E120" s="25" t="inlineStr">
@@ -5646,7 +5631,7 @@
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:Assets · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E121" s="25" t="inlineStr">
@@ -5671,7 +5656,7 @@
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:Assets · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E122" s="25" t="inlineStr">
@@ -5696,7 +5681,7 @@
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:Assets · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E123" s="25" t="inlineStr">
@@ -5721,7 +5706,7 @@
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:Assets · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E124" s="25" t="inlineStr">
@@ -5746,7 +5731,7 @@
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:AccountsPayableCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:Assets · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E125" s="25" t="inlineStr">
@@ -5771,7 +5756,7 @@
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E126" s="25" t="inlineStr">
@@ -5796,7 +5781,7 @@
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E127" s="25" t="inlineStr">
@@ -5821,7 +5806,7 @@
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E128" s="25" t="inlineStr">
@@ -5846,7 +5831,7 @@
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E129" s="25" t="inlineStr">
@@ -5871,7 +5856,7 @@
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:AccountsPayableCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E130" s="25" t="inlineStr">
@@ -5896,7 +5881,7 @@
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E131" s="25" t="inlineStr">
@@ -5921,7 +5906,7 @@
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E132" s="25" t="inlineStr">
@@ -5946,7 +5931,7 @@
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E133" s="25" t="inlineStr">
@@ -5971,7 +5956,7 @@
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E134" s="25" t="inlineStr">
@@ -5996,7 +5981,7 @@
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:Liabilities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:LiabilitiesCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E135" s="25" t="inlineStr">
@@ -6021,7 +6006,7 @@
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:Liabilities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E136" s="25" t="inlineStr">
@@ -6046,7 +6031,7 @@
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:Liabilities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
@@ -6071,7 +6056,7 @@
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:Liabilities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E138" s="25" t="inlineStr">
@@ -6096,7 +6081,7 @@
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:Liabilities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E139" s="25" t="inlineStr">
@@ -6121,7 +6106,7 @@
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:Liabilities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E140" s="25" t="inlineStr">
@@ -6146,7 +6131,7 @@
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E141" s="25" t="inlineStr">
@@ -6171,7 +6156,7 @@
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E142" s="25" t="inlineStr">
@@ -6196,7 +6181,7 @@
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E143" s="25" t="inlineStr">
@@ -6221,7 +6206,7 @@
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E144" s="25" t="inlineStr">
@@ -6246,7 +6231,7 @@
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E145" s="25" t="inlineStr">
@@ -6271,7 +6256,7 @@
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E146" s="25" t="inlineStr">
@@ -6296,7 +6281,7 @@
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E147" s="25" t="inlineStr">
@@ -6321,7 +6306,7 @@
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E148" s="25" t="inlineStr">
@@ -6346,7 +6331,7 @@
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E149" s="25" t="inlineStr">
@@ -6371,7 +6356,7 @@
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+          <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
       <c r="E150" s="25" t="inlineStr">
@@ -6396,7 +6381,7 @@
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
       <c r="E151" s="25" t="inlineStr">
@@ -6421,7 +6406,7 @@
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
       <c r="E152" s="25" t="inlineStr">
@@ -6446,7 +6431,7 @@
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
       <c r="E153" s="25" t="inlineStr">
@@ -6471,7 +6456,7 @@
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
       <c r="E154" s="25" t="inlineStr">
@@ -6496,15 +6481,265 @@
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
+          <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+        </is>
+      </c>
+      <c r="E155" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-25-000079</t>
+        </is>
+      </c>
+      <c r="F155" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="25" t="n">
+        <v>149</v>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2021 10-K</t>
+        </is>
+      </c>
+      <c r="D156" s="25" t="inlineStr">
+        <is>
+          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+        </is>
+      </c>
+      <c r="E156" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-21-000105</t>
+        </is>
+      </c>
+      <c r="F156" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2022 10-K</t>
+        </is>
+      </c>
+      <c r="D157" s="25" t="inlineStr">
+        <is>
+          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+        </is>
+      </c>
+      <c r="E157" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-22-000108</t>
+        </is>
+      </c>
+      <c r="F157" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="25" t="n">
+        <v>151</v>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2023 10-K</t>
+        </is>
+      </c>
+      <c r="D158" s="25" t="inlineStr">
+        <is>
+          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+        </is>
+      </c>
+      <c r="E158" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-23-000106</t>
+        </is>
+      </c>
+      <c r="F158" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="25" t="n">
+        <v>152</v>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2024 10-K</t>
+        </is>
+      </c>
+      <c r="D159" s="25" t="inlineStr">
+        <is>
+          <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+        </is>
+      </c>
+      <c r="E159" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-24-000123</t>
+        </is>
+      </c>
+      <c r="F159" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="25" t="n">
+        <v>153</v>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="D160" s="25" t="inlineStr">
+        <is>
           <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E155" s="25" t="inlineStr">
+      <c r="E160" s="25" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F155" s="26" t="inlineStr">
+      <c r="F160" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="25" t="n">
+        <v>154</v>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2021 10-K</t>
+        </is>
+      </c>
+      <c r="D161" s="25" t="inlineStr">
+        <is>
+          <t>us-gaap:PaymentsOfDividends · period ending 2021-09-25 · USD · filed 2021-10-29</t>
+        </is>
+      </c>
+      <c r="E161" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-21-000105</t>
+        </is>
+      </c>
+      <c r="F161" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="25" t="n">
+        <v>155</v>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2022 10-K</t>
+        </is>
+      </c>
+      <c r="D162" s="25" t="inlineStr">
+        <is>
+          <t>us-gaap:PaymentsOfDividends · period ending 2022-09-24 · USD · filed 2022-10-28</t>
+        </is>
+      </c>
+      <c r="E162" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-22-000108</t>
+        </is>
+      </c>
+      <c r="F162" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="25" t="n">
+        <v>156</v>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2023 10-K</t>
+        </is>
+      </c>
+      <c r="D163" s="25" t="inlineStr">
+        <is>
+          <t>us-gaap:PaymentsOfDividends · period ending 2023-09-30 · USD · filed 2023-11-03</t>
+        </is>
+      </c>
+      <c r="E163" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-23-000106</t>
+        </is>
+      </c>
+      <c r="F163" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="25" t="n">
+        <v>157</v>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2024 10-K</t>
+        </is>
+      </c>
+      <c r="D164" s="25" t="inlineStr">
+        <is>
+          <t>us-gaap:PaymentsOfDividends · period ending 2024-09-28 · USD · filed 2024-11-01</t>
+        </is>
+      </c>
+      <c r="E164" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-24-000123</t>
+        </is>
+      </c>
+      <c r="F164" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="25" t="n">
+        <v>158</v>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>AAPL FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="D165" s="25" t="inlineStr">
+        <is>
+          <t>us-gaap:PaymentsOfDividends · period ending 2025-09-27 · USD · filed 2025-10-31</t>
+        </is>
+      </c>
+      <c r="E165" s="25" t="inlineStr">
+        <is>
+          <t>0000320193-25-000079</t>
+        </is>
+      </c>
+      <c r="F165" s="26" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
@@ -6660,6 +6895,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -7,19 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Profile" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Income Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Filings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Profile" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income Statement" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Balance Sheet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cash Flow" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Filings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Profile'!$B$2:$J$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Income Statement'!$B$2:$J$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Balance Sheet'!$B$2:$J$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cash Flow'!$B$2:$J$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Filings'!$B$2:$F$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Profile'!$A$1:$J$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Income Statement'!$A$1:$J$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Balance Sheet'!$A$1:$J$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash Flow'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Filings'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +35,7 @@
     <numFmt numFmtId="166" formatCode="0.00_);\(0.00\)"/>
     <numFmt numFmtId="167" formatCode="#,##0,,_);\(#,##0,,\)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,13 +125,32 @@
       <sz val="9"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF264D82"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF333333"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -149,8 +170,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,14 +192,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -272,6 +302,216 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1628775" cy="304800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="971550" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="971550" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="971550" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="971550" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="971550" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="971550" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -563,7 +803,300 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J36"/>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="10" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="10" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Company Profile — Apple Inc. (AAPL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Produced by the L3VLUP Company Profile skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Generated 24 August 2026 at 11:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>What this is</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="39" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>A banker one-pager on Apple Inc.: 5 fiscal years of income statement, balance sheet and cash flow exactly as filed, with growth, margins and free cash flow computed live in the workbook so every derived figure can be traced by clicking it. It is the base layer a thesis gets built on, not a thesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>How to read it</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>BLUE  —  a hard input, or a value pulled straight from a filing. Something a human can change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>BLACK  —  a formula computed inside this workbook. Do not overtype it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>GREEN  —  a link to another sheet in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>RED FILL  —  a tie-out that failed. Investigate before using the workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>AN EM DASH  —  the filer did not tag that line. It does not mean zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Every [n] marker beside a row resolves on the Sources tab to a tag, a period, a form and an accession number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Where the numbers come from</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="39" customHeight="1">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Every historic figure is taken from AAPL’s own XBRL tags in its SEC filings (CIK 0000320193), preferring the original annual report for each year over a later filing’s restated comparative. Where the filer did not tag a line, the workbook shows an em dash rather than a zero or an estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Important notices</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="39" customHeight="1">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>EDUCATIONAL USE ONLY. This workbook is produced by L3VLUP as a training and learning aid. It is not investment research, not a recommendation, and not an offer or solicitation to buy or sell any security or financial instrument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="39" customHeight="1">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>NOT INVESTMENT, LEGAL, TAX OR ACCOUNTING ADVICE. Nothing in this file constitutes advice of any kind and it takes no account of the objectives, financial situation or needs of any person. Obtain advice from a suitably qualified and regulated professional before acting on anything here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>NO RELIANCE. The figures are assembled automatically from third-party filings and may be incomplete, mis-tagged at source, superseded by a later restatement, or wrong. Independently verify every figure against the underlying filing — which is why each one is linked — before relying on it for any purpose. Past performance is not a guide to future performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>NO WARRANTY. This workbook is provided “as is” and “as available”, without warranty of any kind, express or implied, including any warranty of accuracy, completeness, merchantability or fitness for a particular purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="65" customHeight="1">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>LIMITATION OF LIABILITY. To the fullest extent permitted by law, L3VLUP and its officers, employees and contributors accept no liability for any loss or damage — including any direct, indirect, incidental, consequential or economic loss, loss of profit, or loss of data — arising out of or in connection with the use of, or reliance on, this workbook or anything in it. Nothing in this notice limits or excludes any liability that cannot lawfully be limited or excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>THIRD-PARTY DATA. Filing data originates from the U.S. Securities and Exchange Commission’s EDGAR system and is in the public domain. The SEC does not endorse, sponsor or verify this workbook. Any figures you enter yourself remain governed by the terms of whichever data provider supplied them, and it is your responsibility to hold the necessary licence for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Copyright</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>© 2026 L3VLUP. All rights reserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>The structure, layout, formulas, wording and conventions of this workbook are the property of L3VLUP. It is licensed to the named recipient for their own personal study and professional work. You may not resell it, redistribute it, publish it, or use it to build or train a competing product or dataset, in whole or in part, without prior written permission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Underlying filing data is public domain and is not claimed as L3VLUP property.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>l3vlup.com  ·  l3vlup.com/skills/company-profile</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B28:H28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -578,649 +1111,685 @@
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Apple Inc. (AAPL)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Company profile</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Source: SEC EDGAR XBRL company facts · CIK 0000320193 · filings only</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>($ in millions, except per share)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>For Fiscal Year Ending</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="D6" s="5" t="inlineStr">
+    <row r="8">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Src</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="9" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D10" s="16" t="n">
         <v>365817000000</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E10" s="16" t="n">
         <v>394328000000</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F10" s="16" t="n">
         <v>383285000000</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G10" s="16" t="n">
         <v>391035000000</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H10" s="16" t="n">
         <v>416161000000</v>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>[1][2][3][4][5]</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="12" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % growth</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="14">
-        <f>IFERROR(E8/D8-1,"")</f>
+      <c r="E11" s="19">
+        <f>IFERROR(E10/D10-1,"")</f>
         <v/>
       </c>
-      <c r="F9" s="14">
-        <f>IFERROR(F8/E8-1,"")</f>
+      <c r="F11" s="19">
+        <f>IFERROR(F10/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="14">
-        <f>IFERROR(G8/F8-1,"")</f>
+      <c r="G11" s="19">
+        <f>IFERROR(G10/F10-1,"")</f>
         <v/>
       </c>
-      <c r="H9" s="14">
-        <f>IFERROR(H8/G8-1,"")</f>
+      <c r="H11" s="19">
+        <f>IFERROR(H10/G10-1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="9" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D12" s="16" t="n">
         <v>152836000000</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E12" s="16" t="n">
         <v>170782000000</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F12" s="16" t="n">
         <v>169148000000</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G12" s="16" t="n">
         <v>180683000000</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H12" s="16" t="n">
         <v>195201000000</v>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>[6][7][8][9][10]</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="12" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % margin</t>
         </is>
       </c>
-      <c r="D11" s="14">
-        <f>IFERROR(D10/D8,"")</f>
+      <c r="D13" s="19">
+        <f>IFERROR(D12/D10,"")</f>
         <v/>
       </c>
-      <c r="E11" s="14">
-        <f>IFERROR(E10/E8,"")</f>
+      <c r="E13" s="19">
+        <f>IFERROR(E12/E10,"")</f>
         <v/>
       </c>
-      <c r="F11" s="14">
-        <f>IFERROR(F10/F8,"")</f>
+      <c r="F13" s="19">
+        <f>IFERROR(F12/F10,"")</f>
         <v/>
       </c>
-      <c r="G11" s="14">
-        <f>IFERROR(G10/G8,"")</f>
+      <c r="G13" s="19">
+        <f>IFERROR(G12/G10,"")</f>
         <v/>
       </c>
-      <c r="H11" s="14">
-        <f>IFERROR(H10/H8,"")</f>
+      <c r="H13" s="19">
+        <f>IFERROR(H12/H10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="9" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Operating income</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D14" s="16" t="n">
         <v>108949000000</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E14" s="16" t="n">
         <v>119437000000</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F14" s="16" t="n">
         <v>114301000000</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G14" s="16" t="n">
         <v>123216000000</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H14" s="16" t="n">
         <v>133050000000</v>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>[11][12][13][14][15]</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="12" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % margin</t>
         </is>
       </c>
-      <c r="D13" s="14">
-        <f>IFERROR(D12/D8,"")</f>
+      <c r="D15" s="19">
+        <f>IFERROR(D14/D10,"")</f>
         <v/>
       </c>
-      <c r="E13" s="14">
-        <f>IFERROR(E12/E8,"")</f>
+      <c r="E15" s="19">
+        <f>IFERROR(E14/E10,"")</f>
         <v/>
       </c>
-      <c r="F13" s="14">
-        <f>IFERROR(F12/F8,"")</f>
+      <c r="F15" s="19">
+        <f>IFERROR(F14/F10,"")</f>
         <v/>
       </c>
-      <c r="G13" s="14">
-        <f>IFERROR(G12/G8,"")</f>
+      <c r="G15" s="19">
+        <f>IFERROR(G14/G10,"")</f>
         <v/>
       </c>
-      <c r="H13" s="14">
-        <f>IFERROR(H12/H8,"")</f>
+      <c r="H15" s="19">
+        <f>IFERROR(H14/H10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D16" s="16" t="n">
         <v>94680000000</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E16" s="16" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F16" s="16" t="n">
         <v>96995000000</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G16" s="16" t="n">
         <v>93736000000</v>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="H16" s="16" t="n">
         <v>112010000000</v>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>[16][17][18][19][20]</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="12" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % margin</t>
         </is>
       </c>
-      <c r="D15" s="14">
-        <f>IFERROR(D14/D8,"")</f>
+      <c r="D17" s="19">
+        <f>IFERROR(D16/D10,"")</f>
         <v/>
       </c>
-      <c r="E15" s="14">
-        <f>IFERROR(E14/E8,"")</f>
+      <c r="E17" s="19">
+        <f>IFERROR(E16/E10,"")</f>
         <v/>
       </c>
-      <c r="F15" s="14">
-        <f>IFERROR(F14/F8,"")</f>
+      <c r="F17" s="19">
+        <f>IFERROR(F16/F10,"")</f>
         <v/>
       </c>
-      <c r="G15" s="14">
-        <f>IFERROR(G14/G8,"")</f>
+      <c r="G17" s="19">
+        <f>IFERROR(G16/G10,"")</f>
         <v/>
       </c>
-      <c r="H15" s="14">
-        <f>IFERROR(H14/H8,"")</f>
+      <c r="H17" s="19">
+        <f>IFERROR(H16/H10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Per share</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr">
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D20" s="20" t="n">
         <v>5.61</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E20" s="20" t="n">
         <v>6.11</v>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F20" s="20" t="n">
         <v>6.13</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G20" s="20" t="n">
         <v>6.08</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H20" s="20" t="n">
         <v>7.46</v>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>[21][22][23][24][25]</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="9" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D21" s="21" t="n">
         <v>16864919000</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E21" s="21" t="n">
         <v>16325819000</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F21" s="21" t="n">
         <v>15812547000</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G21" s="21" t="n">
         <v>15408095000</v>
       </c>
-      <c r="H19" s="16" t="n">
+      <c r="H21" s="21" t="n">
         <v>15004697000</v>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>[26][27][28][29][30]</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Cash generation</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="9" t="inlineStr">
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D24" s="16" t="n">
         <v>104038000000</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E24" s="16" t="n">
         <v>122151000000</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F24" s="16" t="n">
         <v>110543000000</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G24" s="16" t="n">
         <v>118254000000</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H24" s="16" t="n">
         <v>111482000000</v>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>[31][32][33][34][35]</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="9" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D25" s="16" t="n">
         <v>11085000000</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E25" s="16" t="n">
         <v>10708000000</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F25" s="16" t="n">
         <v>10959000000</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G25" s="16" t="n">
         <v>9447000000</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H25" s="16" t="n">
         <v>12715000000</v>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J25" s="17" t="inlineStr">
         <is>
           <t>[36][37][38][39][40]</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="17" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="D24" s="18">
-        <f>IFERROR(D22-D23,"")</f>
+      <c r="D26" s="23">
+        <f>IFERROR(D24-D25,"")</f>
         <v/>
       </c>
-      <c r="E24" s="18">
-        <f>IFERROR(E22-E23,"")</f>
+      <c r="E26" s="23">
+        <f>IFERROR(E24-E25,"")</f>
         <v/>
       </c>
-      <c r="F24" s="18">
-        <f>IFERROR(F22-F23,"")</f>
+      <c r="F26" s="23">
+        <f>IFERROR(F24-F25,"")</f>
         <v/>
       </c>
-      <c r="G24" s="18">
-        <f>IFERROR(G22-G23,"")</f>
+      <c r="G26" s="23">
+        <f>IFERROR(G24-G25,"")</f>
         <v/>
       </c>
-      <c r="H24" s="18">
-        <f>IFERROR(H22-H23,"")</f>
+      <c r="H26" s="23">
+        <f>IFERROR(H24-H25,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="12" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % of revenue</t>
         </is>
       </c>
-      <c r="D25" s="14">
-        <f>IFERROR(D24/D8,"")</f>
+      <c r="D27" s="19">
+        <f>IFERROR(D26/D10,"")</f>
         <v/>
       </c>
-      <c r="E25" s="14">
-        <f>IFERROR(E24/E8,"")</f>
+      <c r="E27" s="19">
+        <f>IFERROR(E26/E10,"")</f>
         <v/>
       </c>
-      <c r="F25" s="14">
-        <f>IFERROR(F24/F8,"")</f>
+      <c r="F27" s="19">
+        <f>IFERROR(F26/F10,"")</f>
         <v/>
       </c>
-      <c r="G25" s="14">
-        <f>IFERROR(G24/G8,"")</f>
+      <c r="G27" s="19">
+        <f>IFERROR(G26/G10,"")</f>
         <v/>
       </c>
-      <c r="H25" s="14">
-        <f>IFERROR(H24/H8,"")</f>
+      <c r="H27" s="19">
+        <f>IFERROR(H26/H10,"")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="7" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Balance sheet</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Cash and equivalents</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D30" s="16" t="n">
         <v>34940000000</v>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="E30" s="16" t="n">
         <v>23646000000</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F30" s="16" t="n">
         <v>29965000000</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G30" s="16" t="n">
         <v>29943000000</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H30" s="16" t="n">
         <v>35934000000</v>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>[41][42][43][44][45]</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="9" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Short-term investments</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D31" s="16" t="n">
         <v>27699000000</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E31" s="16" t="n">
         <v>24658000000</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F31" s="16" t="n">
         <v>31590000000</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G31" s="16" t="n">
         <v>35228000000</v>
       </c>
-      <c r="H29" s="10" t="n">
+      <c r="H31" s="16" t="n">
         <v>18763000000</v>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J31" s="17" t="inlineStr">
         <is>
           <t>[46][47][48][49][50]</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="9" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Total debt</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D32" s="16" t="n">
         <v>127676000000</v>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E32" s="16" t="n">
         <v>122952000000</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F32" s="16" t="n">
         <v>116394000000</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G32" s="16" t="n">
         <v>108253000000</v>
       </c>
-      <c r="H30" s="10" t="n">
+      <c r="H32" s="16" t="n">
         <v>103631000000</v>
       </c>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>[51][52][53][54][55]</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="17" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>Net debt / (net cash)</t>
         </is>
       </c>
-      <c r="D31" s="19" t="n">
+      <c r="D33" s="24" t="n">
         <v>65037000000</v>
       </c>
-      <c r="E31" s="19" t="n">
+      <c r="E33" s="24" t="n">
         <v>74648000000</v>
       </c>
-      <c r="F31" s="19" t="n">
+      <c r="F33" s="24" t="n">
         <v>54839000000</v>
       </c>
-      <c r="G31" s="19" t="n">
+      <c r="G33" s="24" t="n">
         <v>43082000000</v>
       </c>
-      <c r="H31" s="19" t="n">
+      <c r="H33" s="24" t="n">
         <v>48934000000</v>
       </c>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="J33" s="17" t="inlineStr">
         <is>
           <t>[56][57][58][59][60]</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="9" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Total shareholders' equity</t>
         </is>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D34" s="16" t="n">
         <v>63090000000</v>
       </c>
-      <c r="E32" s="10" t="n">
+      <c r="E34" s="16" t="n">
         <v>50672000000</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F34" s="16" t="n">
         <v>62146000000</v>
       </c>
-      <c r="G32" s="10" t="n">
+      <c r="G34" s="16" t="n">
         <v>56950000000</v>
       </c>
-      <c r="H32" s="10" t="n">
+      <c r="H34" s="16" t="n">
         <v>73733000000</v>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t>[61][62][63][64][65]</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="20" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>Blue = value as tagged in the filing. Black = formula computed in this workbook.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="20" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>An em dash means the filer did not tag that line. It does not mean zero.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="20" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>Not tagged by this filer: minority_interest</t>
         </is>
@@ -1229,16 +1798,25 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K808080L3VLUP&amp;R&amp;8 &amp;K808080Page &amp;P of &amp;N — see Cover for notices</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1253,467 +1831,512 @@
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Apple Inc. (AAPL)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Income statement</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>As reported in the filings — original filing preferred over a later restatement's comparative</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>($ in millions, except per share)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>For Fiscal Year Ending</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="D6" s="5" t="inlineStr">
+    <row r="8">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Src</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="17" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D9" s="24" t="n">
         <v>365817000000</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E9" s="24" t="n">
         <v>394328000000</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F9" s="24" t="n">
         <v>383285000000</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G9" s="24" t="n">
         <v>391035000000</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H9" s="24" t="n">
         <v>416161000000</v>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>[1][2][3][4][5]</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % growth</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="14">
-        <f>IFERROR(E7/D7-1,"")</f>
+      <c r="E10" s="19">
+        <f>IFERROR(E9/D9-1,"")</f>
         <v/>
       </c>
-      <c r="F8" s="14">
-        <f>IFERROR(F7/E7-1,"")</f>
+      <c r="F10" s="19">
+        <f>IFERROR(F9/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="14">
-        <f>IFERROR(G7/F7-1,"")</f>
+      <c r="G10" s="19">
+        <f>IFERROR(G9/F9-1,"")</f>
         <v/>
       </c>
-      <c r="H8" s="14">
-        <f>IFERROR(H7/G7-1,"")</f>
+      <c r="H10" s="19">
+        <f>IFERROR(H9/G9-1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="9" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Cost of revenue</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D11" s="16" t="n">
         <v>212981000000</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E11" s="16" t="n">
         <v>223546000000</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F11" s="16" t="n">
         <v>214137000000</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G11" s="16" t="n">
         <v>210352000000</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H11" s="16" t="n">
         <v>220960000000</v>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>[66][67][68][69][70]</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="17" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D12" s="24" t="n">
         <v>152836000000</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E12" s="24" t="n">
         <v>170782000000</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F12" s="24" t="n">
         <v>169148000000</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G12" s="24" t="n">
         <v>180683000000</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H12" s="24" t="n">
         <v>195201000000</v>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>[6][7][8][9][10]</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="12" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % margin</t>
         </is>
       </c>
-      <c r="D11" s="14">
-        <f>IFERROR(D10/D7,"")</f>
+      <c r="D13" s="19">
+        <f>IFERROR(D12/D9,"")</f>
         <v/>
       </c>
-      <c r="E11" s="14">
-        <f>IFERROR(E10/E7,"")</f>
+      <c r="E13" s="19">
+        <f>IFERROR(E12/E9,"")</f>
         <v/>
       </c>
-      <c r="F11" s="14">
-        <f>IFERROR(F10/F7,"")</f>
+      <c r="F13" s="19">
+        <f>IFERROR(F12/F9,"")</f>
         <v/>
       </c>
-      <c r="G11" s="14">
-        <f>IFERROR(G10/G7,"")</f>
+      <c r="G13" s="19">
+        <f>IFERROR(G12/G9,"")</f>
         <v/>
       </c>
-      <c r="H11" s="14">
-        <f>IFERROR(H10/H7,"")</f>
+      <c r="H13" s="19">
+        <f>IFERROR(H12/H9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="9" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Research and development</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D14" s="16" t="n">
         <v>21914000000</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E14" s="16" t="n">
         <v>26251000000</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F14" s="16" t="n">
         <v>29915000000</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G14" s="16" t="n">
         <v>31370000000</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H14" s="16" t="n">
         <v>34550000000</v>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>[71][72][73][74][75]</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="9" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Selling, general and administrative</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D15" s="16" t="n">
         <v>21973000000</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E15" s="16" t="n">
         <v>25094000000</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F15" s="16" t="n">
         <v>24932000000</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G15" s="16" t="n">
         <v>26097000000</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="H15" s="16" t="n">
         <v>27601000000</v>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>[76][77][78][79][80]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Operating income</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D16" s="24" t="n">
         <v>108949000000</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E16" s="24" t="n">
         <v>119437000000</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F16" s="24" t="n">
         <v>114301000000</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G16" s="24" t="n">
         <v>123216000000</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H16" s="24" t="n">
         <v>133050000000</v>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>[11][12][13][14][15]</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="12" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % margin</t>
         </is>
       </c>
-      <c r="D15" s="14">
-        <f>IFERROR(D14/D7,"")</f>
+      <c r="D17" s="19">
+        <f>IFERROR(D16/D9,"")</f>
         <v/>
       </c>
-      <c r="E15" s="14">
-        <f>IFERROR(E14/E7,"")</f>
+      <c r="E17" s="19">
+        <f>IFERROR(E16/E9,"")</f>
         <v/>
       </c>
-      <c r="F15" s="14">
-        <f>IFERROR(F14/F7,"")</f>
+      <c r="F17" s="19">
+        <f>IFERROR(F16/F9,"")</f>
         <v/>
       </c>
-      <c r="G15" s="14">
-        <f>IFERROR(G14/G7,"")</f>
+      <c r="G17" s="19">
+        <f>IFERROR(G16/G9,"")</f>
         <v/>
       </c>
-      <c r="H15" s="14">
-        <f>IFERROR(H14/H7,"")</f>
+      <c r="H17" s="19">
+        <f>IFERROR(H16/H9,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Interest expense</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D18" s="16" t="n">
         <v>2645000000</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E18" s="16" t="n">
         <v>2931000000</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F18" s="16" t="n">
         <v>3933000000</v>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G18" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>[81][82][83]</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="9" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Pre-tax income</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D19" s="16" t="n">
         <v>109207000000</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E19" s="16" t="n">
         <v>119103000000</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F19" s="16" t="n">
         <v>113736000000</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G19" s="16" t="n">
         <v>123485000000</v>
       </c>
-      <c r="H17" s="10" t="n">
+      <c r="H19" s="16" t="n">
         <v>132729000000</v>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>[84][85][86][87][88]</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Income tax expense</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D20" s="16" t="n">
         <v>14527000000</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E20" s="16" t="n">
         <v>19300000000</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F20" s="16" t="n">
         <v>16741000000</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G20" s="16" t="n">
         <v>29749000000</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="H20" s="16" t="n">
         <v>20719000000</v>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>[89][90][91][92][93]</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="17" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D21" s="24" t="n">
         <v>94680000000</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E21" s="24" t="n">
         <v>99803000000</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F21" s="24" t="n">
         <v>96995000000</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G21" s="24" t="n">
         <v>93736000000</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H21" s="24" t="n">
         <v>112010000000</v>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>[16][17][18][19][20]</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="12" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % margin</t>
         </is>
       </c>
-      <c r="D20" s="14">
-        <f>IFERROR(D19/D7,"")</f>
+      <c r="D22" s="19">
+        <f>IFERROR(D21/D9,"")</f>
         <v/>
       </c>
-      <c r="E20" s="14">
-        <f>IFERROR(E19/E7,"")</f>
+      <c r="E22" s="19">
+        <f>IFERROR(E21/E9,"")</f>
         <v/>
       </c>
-      <c r="F20" s="14">
-        <f>IFERROR(F19/F7,"")</f>
+      <c r="F22" s="19">
+        <f>IFERROR(F21/F9,"")</f>
         <v/>
       </c>
-      <c r="G20" s="14">
-        <f>IFERROR(G19/G7,"")</f>
+      <c r="G22" s="19">
+        <f>IFERROR(G21/G9,"")</f>
         <v/>
       </c>
-      <c r="H20" s="14">
-        <f>IFERROR(H19/H7,"")</f>
+      <c r="H22" s="19">
+        <f>IFERROR(H21/H9,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K808080L3VLUP&amp;R&amp;8 &amp;K808080Page &amp;P of &amp;N — see Cover for notices</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1728,533 +2351,578 @@
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Apple Inc. (AAPL)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Balance sheet</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>As reported in the filings — original filing preferred over a later restatement's comparative</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>($ in millions, except per share)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>For Fiscal Year Ending</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="D6" s="5" t="inlineStr">
+    <row r="8">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Src</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="9" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Cash and equivalents</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D9" s="16" t="n">
         <v>34940000000</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E9" s="16" t="n">
         <v>23646000000</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F9" s="16" t="n">
         <v>29965000000</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G9" s="16" t="n">
         <v>29943000000</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H9" s="16" t="n">
         <v>35934000000</v>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>[41][42][43][44][45]</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="9" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Short-term investments</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D10" s="16" t="n">
         <v>27699000000</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E10" s="16" t="n">
         <v>24658000000</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F10" s="16" t="n">
         <v>31590000000</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G10" s="16" t="n">
         <v>35228000000</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H10" s="16" t="n">
         <v>18763000000</v>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>[46][47][48][49][50]</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="9" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Accounts receivable</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D11" s="16" t="n">
         <v>26278000000</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E11" s="16" t="n">
         <v>28184000000</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F11" s="16" t="n">
         <v>29508000000</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G11" s="16" t="n">
         <v>33410000000</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H11" s="16" t="n">
         <v>39777000000</v>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>[94][95][96][97][98]</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="9" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D12" s="16" t="n">
         <v>6580000000</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E12" s="16" t="n">
         <v>4946000000</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F12" s="16" t="n">
         <v>6331000000</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G12" s="16" t="n">
         <v>7286000000</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H12" s="16" t="n">
         <v>5718000000</v>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>[99][100][101][102][103]</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D13" s="24" t="n">
         <v>134836000000</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E13" s="24" t="n">
         <v>135405000000</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F13" s="24" t="n">
         <v>143566000000</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G13" s="24" t="n">
         <v>152987000000</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H13" s="24" t="n">
         <v>147957000000</v>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>[104][105][106][107][108]</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="9" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Property, plant and equipment, net</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D14" s="16" t="n">
         <v>39440000000</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E14" s="16" t="n">
         <v>42117000000</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F14" s="16" t="n">
         <v>43715000000</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G14" s="16" t="n">
         <v>45680000000</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H14" s="16" t="n">
         <v>49834000000</v>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>[109][110][111][112][113]</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="9" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F15" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G15" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D16" s="24" t="n">
         <v>351002000000</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E16" s="24" t="n">
         <v>352755000000</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F16" s="24" t="n">
         <v>352583000000</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G16" s="24" t="n">
         <v>364980000000</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H16" s="24" t="n">
         <v>359241000000</v>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>[114][115][116][117][118]</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="9" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D17" s="16" t="n">
         <v>54763000000</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E17" s="16" t="n">
         <v>64115000000</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F17" s="16" t="n">
         <v>62611000000</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G17" s="16" t="n">
         <v>68960000000</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H17" s="16" t="n">
         <v>69860000000</v>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>[119][120][121][122][123]</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D18" s="24" t="n">
         <v>125481000000</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E18" s="24" t="n">
         <v>153982000000</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F18" s="24" t="n">
         <v>145308000000</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G18" s="24" t="n">
         <v>176392000000</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H18" s="24" t="n">
         <v>165631000000</v>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>[124][125][126][127][128]</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="9" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Short-term debt</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D19" s="16" t="n">
         <v>9613000000</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E19" s="16" t="n">
         <v>11128000000</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F19" s="16" t="n">
         <v>9822000000</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G19" s="16" t="n">
         <v>10912000000</v>
       </c>
-      <c r="H17" s="10" t="n">
+      <c r="H19" s="16" t="n">
         <v>12350000000</v>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>[56][57][58][59][60]</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Long-term debt</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D20" s="16" t="n">
         <v>118063000000</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E20" s="16" t="n">
         <v>111824000000</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F20" s="16" t="n">
         <v>106572000000</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G20" s="16" t="n">
         <v>97341000000</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="H20" s="16" t="n">
         <v>91281000000</v>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>[51][52][53][54][55]</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="17" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D21" s="24" t="n">
         <v>287912000000</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E21" s="24" t="n">
         <v>302083000000</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F21" s="24" t="n">
         <v>290437000000</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G21" s="24" t="n">
         <v>308030000000</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H21" s="24" t="n">
         <v>285508000000</v>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>[129][130][131][132][133]</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="17" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>Total shareholders' equity</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D22" s="24" t="n">
         <v>63090000000</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E22" s="24" t="n">
         <v>50672000000</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F22" s="24" t="n">
         <v>62146000000</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G22" s="24" t="n">
         <v>56950000000</v>
       </c>
-      <c r="H20" s="19" t="n">
+      <c r="H22" s="24" t="n">
         <v>73733000000</v>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>[61][62][63][64][65]</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="17" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>Total liabilities and equity</t>
         </is>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D24" s="24" t="n">
         <v>351002000000</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E24" s="24" t="n">
         <v>352755000000</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F24" s="24" t="n">
         <v>352583000000</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G24" s="24" t="n">
         <v>364980000000</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H24" s="24" t="n">
         <v>359241000000</v>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>[134][135][136][137][138]</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="12" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Balance check (assets less liabilities and equity)</t>
         </is>
       </c>
-      <c r="D23" s="22">
-        <f>IFERROR(ROUND(D14-D22,0),0)</f>
+      <c r="D25" s="27">
+        <f>IFERROR(ROUND(D16-D24,0),0)</f>
         <v/>
       </c>
-      <c r="E23" s="22">
-        <f>IFERROR(ROUND(E14-E22,0),0)</f>
+      <c r="E25" s="27">
+        <f>IFERROR(ROUND(E16-E24,0),0)</f>
         <v/>
       </c>
-      <c r="F23" s="22">
-        <f>IFERROR(ROUND(F14-F22,0),0)</f>
+      <c r="F25" s="27">
+        <f>IFERROR(ROUND(F16-F24,0),0)</f>
         <v/>
       </c>
-      <c r="G23" s="22">
-        <f>IFERROR(ROUND(G14-G22,0),0)</f>
+      <c r="G25" s="27">
+        <f>IFERROR(ROUND(G16-G24,0),0)</f>
         <v/>
       </c>
-      <c r="H23" s="22">
-        <f>IFERROR(ROUND(H14-H22,0),0)</f>
+      <c r="H25" s="27">
+        <f>IFERROR(ROUND(H16-H24,0),0)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="20" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>A non-zero balance check is highlighted red. It means the filer's tagged totals do not tie, and the workbook should not be used until the discrepancy is understood.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D23:H23">
+  <conditionalFormatting sqref="D25:H25">
     <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K808080L3VLUP&amp;R&amp;8 &amp;K808080Page &amp;P of &amp;N — see Cover for notices</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2269,273 +2937,318 @@
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Apple Inc. (AAPL)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Cash flow statement</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>As reported in the filings — original filing preferred over a later restatement's comparative</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>($ in millions, except per share)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>For Fiscal Year Ending</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="D6" s="5" t="inlineStr">
+    <row r="8">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Src</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="17" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D9" s="24" t="n">
         <v>104038000000</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E9" s="24" t="n">
         <v>122151000000</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F9" s="24" t="n">
         <v>110543000000</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G9" s="24" t="n">
         <v>118254000000</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H9" s="24" t="n">
         <v>111482000000</v>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>[31][32][33][34][35]</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="9" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D10" s="16" t="n">
         <v>11085000000</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E10" s="16" t="n">
         <v>10708000000</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F10" s="16" t="n">
         <v>10959000000</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G10" s="16" t="n">
         <v>9447000000</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H10" s="16" t="n">
         <v>12715000000</v>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>[36][37][38][39][40]</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="9" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Cash from investing</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D11" s="16" t="n">
         <v>-14545000000</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E11" s="16" t="n">
         <v>-22354000000</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F11" s="16" t="n">
         <v>3705000000</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G11" s="16" t="n">
         <v>2935000000</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H11" s="16" t="n">
         <v>15195000000</v>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>[139][140][141][142][143]</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="9" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Cash from financing</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D12" s="16" t="n">
         <v>-93353000000</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E12" s="16" t="n">
         <v>-110749000000</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F12" s="16" t="n">
         <v>-108488000000</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G12" s="16" t="n">
         <v>-121983000000</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H12" s="16" t="n">
         <v>-120686000000</v>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>[144][145][146][147][148]</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="9" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D13" s="16" t="n">
         <v>85971000000</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E13" s="16" t="n">
         <v>89402000000</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F13" s="16" t="n">
         <v>77550000000</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G13" s="16" t="n">
         <v>94949000000</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H13" s="16" t="n">
         <v>90711000000</v>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>[149][150][151][152][153]</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="9" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Dividends paid</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D14" s="16" t="n">
         <v>14467000000</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E14" s="16" t="n">
         <v>14841000000</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F14" s="16" t="n">
         <v>15025000000</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G14" s="16" t="n">
         <v>15234000000</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H14" s="16" t="n">
         <v>15421000000</v>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>[154][155][156][157][158]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="D14" s="18">
-        <f>IFERROR(D7-D8,"")</f>
+      <c r="D16" s="23">
+        <f>IFERROR(D9-D10,"")</f>
         <v/>
       </c>
-      <c r="E14" s="18">
-        <f>IFERROR(E7-E8,"")</f>
+      <c r="E16" s="23">
+        <f>IFERROR(E9-E10,"")</f>
         <v/>
       </c>
-      <c r="F14" s="18">
-        <f>IFERROR(F7-F8,"")</f>
+      <c r="F16" s="23">
+        <f>IFERROR(F9-F10,"")</f>
         <v/>
       </c>
-      <c r="G14" s="18">
-        <f>IFERROR(G7-G8,"")</f>
+      <c r="G16" s="23">
+        <f>IFERROR(G9-G10,"")</f>
         <v/>
       </c>
-      <c r="H14" s="18">
-        <f>IFERROR(H7-H8,"")</f>
+      <c r="H16" s="23">
+        <f>IFERROR(H9-H10,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K808080L3VLUP&amp;R&amp;8 &amp;K808080Page &amp;P of &amp;N — see Cover for notices</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2545,173 +3258,197 @@
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Apple Inc. (AAPL)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Filings used</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>The primary documents behind every figure in this workbook</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Recent annual and quarterly filings</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="9" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>10-Q · period 2026-06-27 · filed 2026-07-31</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>0000320193-26-000020</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="9" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>10-Q · period 2026-03-28 · filed 2026-05-01</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>0000320193-26-000013</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="9" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>10-Q · period 2025-12-27 · filed 2026-01-30</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>0000320193-26-000006</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="9" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>10-K · period 2025-09-27 · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="9" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>10-Q · period 2025-06-28 · filed 2025-08-01</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>0000320193-25-000073</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="9" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>10-Q · period 2025-03-29 · filed 2025-05-02</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>0000320193-25-000057</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>10-Q · period 2024-12-28 · filed 2025-01-31</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>0000320193-25-000008</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="9" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>10-K · period 2024-09-28 · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>10-Q · period 2024-06-29 · filed 2024-08-02</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>0000320193-24-000081</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="9" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>10-Q · period 2024-03-30 · filed 2024-05-03</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>0000320193-24-000069</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>10-Q · period 2023-12-30 · filed 2024-02-02</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>0000320193-24-000006</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="9" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>10-K · period 2023-09-30 · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
@@ -2720,16 +3457,25 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;8 &amp;K808080L3VLUP&amp;R&amp;8 &amp;K808080Page &amp;P of &amp;N — see Cover for notices</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F165"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2740,4006 +3486,4030 @@
     <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Apple Inc. (AAPL)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Sources and audit trail</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Every marker in the [n] column of any tab resolves here. Historic financials come from filings, never from an aggregator.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="24" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Some lines are blank because the filer did not tag them — see the Profile tab note.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Accession</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="25" t="n">
+    <row r="9">
+      <c r="B9" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="25" t="n">
+    <row r="10">
+      <c r="B10" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="25" t="n">
+    <row r="11">
+      <c r="B11" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="25" t="n">
+    <row r="12">
+      <c r="B12" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F12" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="25" t="n">
+    <row r="13">
+      <c r="B13" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>us-gaap:RevenueFromContractWithCustomerExcludingAssessedTax · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F13" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="25" t="n">
+    <row r="14">
+      <c r="B14" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F14" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="25" t="n">
+    <row r="15">
+      <c r="B15" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F15" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="25" t="n">
+    <row r="16">
+      <c r="B16" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="25" t="n">
+    <row r="17">
+      <c r="B17" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F17" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="25" t="n">
+    <row r="18">
+      <c r="B18" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>us-gaap:GrossProfit · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="25" t="n">
+    <row r="19">
+      <c r="B19" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F19" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="25" t="n">
+    <row r="20">
+      <c r="B20" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="25" t="n">
+    <row r="21">
+      <c r="B21" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F21" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="25" t="n">
+    <row r="22">
+      <c r="B22" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F22" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="25" t="n">
+    <row r="23">
+      <c r="B23" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>us-gaap:OperatingIncomeLoss · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F23" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="25" t="n">
+    <row r="24">
+      <c r="B24" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F24" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="25" t="n">
+    <row r="25">
+      <c r="B25" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F25" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="25" t="n">
+    <row r="26">
+      <c r="B26" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F25" s="26" t="inlineStr">
+      <c r="F26" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="25" t="n">
+    <row r="27">
+      <c r="B27" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="25" t="n">
+    <row r="28">
+      <c r="B28" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetIncomeLoss · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="F28" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="25" t="n">
+    <row r="29">
+      <c r="B29" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2021-09-25 · USD/shares · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F29" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="25" t="n">
+    <row r="30">
+      <c r="B30" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2022-09-24 · USD/shares · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F29" s="26" t="inlineStr">
+      <c r="F30" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="25" t="n">
+    <row r="31">
+      <c r="B31" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2023-09-30 · USD/shares · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F31" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="25" t="n">
+    <row r="32">
+      <c r="B32" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D32" s="30" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2024-09-28 · USD/shares · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E32" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="F32" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="25" t="n">
+    <row r="33">
+      <c r="B33" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted · period ending 2025-09-27 · USD/shares · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F33" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="25" t="n">
+    <row r="34">
+      <c r="B34" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2021-09-25 · shares · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F33" s="26" t="inlineStr">
+      <c r="F34" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="25" t="n">
+    <row r="35">
+      <c r="B35" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2022-09-24 · shares · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E34" s="25" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="F35" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="25" t="n">
+    <row r="36">
+      <c r="B36" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2023-09-30 · shares · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F35" s="26" t="inlineStr">
+      <c r="F36" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="25" t="n">
+    <row r="37">
+      <c r="B37" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D37" s="30" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2024-09-28 · shares · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="F37" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="25" t="n">
+    <row r="38">
+      <c r="B38" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr">
         <is>
           <t>us-gaap:WeightedAverageNumberOfDilutedSharesOutstanding · period ending 2025-09-27 · shares · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F37" s="26" t="inlineStr">
+      <c r="F38" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="25" t="n">
+    <row r="39">
+      <c r="B39" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D38" s="25" t="inlineStr">
+      <c r="D39" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="E39" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F38" s="26" t="inlineStr">
+      <c r="F39" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="25" t="n">
+    <row r="40">
+      <c r="B40" s="30" t="n">
         <v>32</v>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D40" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="F40" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="25" t="n">
+    <row r="41">
+      <c r="B41" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D41" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="E41" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="F41" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="25" t="n">
+    <row r="42">
+      <c r="B42" s="30" t="n">
         <v>34</v>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
+      <c r="D42" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E42" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="F42" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="25" t="n">
+    <row r="43">
+      <c r="B43" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="D43" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInOperatingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
+      <c r="E43" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F42" s="26" t="inlineStr">
+      <c r="F43" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="25" t="n">
+    <row r="44">
+      <c r="B44" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D43" s="25" t="inlineStr">
+      <c r="D44" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="E44" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F43" s="26" t="inlineStr">
+      <c r="F44" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="25" t="n">
+    <row r="45">
+      <c r="B45" s="30" t="n">
         <v>37</v>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D44" s="25" t="inlineStr">
+      <c r="D45" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E44" s="25" t="inlineStr">
+      <c r="E45" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F44" s="26" t="inlineStr">
+      <c r="F45" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="25" t="n">
+    <row r="46">
+      <c r="B46" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D45" s="25" t="inlineStr">
+      <c r="D46" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="E46" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F45" s="26" t="inlineStr">
+      <c r="F46" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="25" t="n">
+    <row r="47">
+      <c r="B47" s="30" t="n">
         <v>39</v>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D46" s="25" t="inlineStr">
+      <c r="D47" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E46" s="25" t="inlineStr">
+      <c r="E47" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F46" s="26" t="inlineStr">
+      <c r="F47" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="25" t="n">
+    <row r="48">
+      <c r="B48" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D47" s="25" t="inlineStr">
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsToAcquirePropertyPlantAndEquipment · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="E48" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F47" s="26" t="inlineStr">
+      <c r="F48" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="25" t="n">
+    <row r="49">
+      <c r="B49" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D48" s="25" t="inlineStr">
+      <c r="D49" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E48" s="25" t="inlineStr">
+      <c r="E49" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F48" s="26" t="inlineStr">
+      <c r="F49" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="25" t="n">
+    <row r="50">
+      <c r="B50" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D49" s="25" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="E50" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F49" s="26" t="inlineStr">
+      <c r="F50" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="25" t="n">
+    <row r="51">
+      <c r="B51" s="30" t="n">
         <v>43</v>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C51" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D50" s="25" t="inlineStr">
+      <c r="D51" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E50" s="25" t="inlineStr">
+      <c r="E51" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F50" s="26" t="inlineStr">
+      <c r="F51" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="25" t="n">
+    <row r="52">
+      <c r="B52" s="30" t="n">
         <v>44</v>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D51" s="25" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="E52" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F51" s="26" t="inlineStr">
+      <c r="F52" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="25" t="n">
+    <row r="53">
+      <c r="B53" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D52" s="25" t="inlineStr">
+      <c r="D53" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CashAndCashEquivalentsAtCarryingValue · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E52" s="25" t="inlineStr">
+      <c r="E53" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F52" s="26" t="inlineStr">
+      <c r="F53" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="25" t="n">
+    <row r="54">
+      <c r="B54" s="30" t="n">
         <v>46</v>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D53" s="25" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>us-gaap:MarketableSecuritiesCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="E54" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F53" s="26" t="inlineStr">
+      <c r="F54" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="25" t="n">
+    <row r="55">
+      <c r="B55" s="30" t="n">
         <v>47</v>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D54" s="25" t="inlineStr">
+      <c r="D55" s="30" t="inlineStr">
         <is>
           <t>us-gaap:MarketableSecuritiesCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E54" s="25" t="inlineStr">
+      <c r="E55" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F54" s="26" t="inlineStr">
+      <c r="F55" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="25" t="n">
+    <row r="56">
+      <c r="B56" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C56" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D55" s="25" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>us-gaap:MarketableSecuritiesCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="E56" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F55" s="26" t="inlineStr">
+      <c r="F56" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="25" t="n">
+    <row r="57">
+      <c r="B57" s="30" t="n">
         <v>49</v>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C57" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D56" s="25" t="inlineStr">
+      <c r="D57" s="30" t="inlineStr">
         <is>
           <t>us-gaap:MarketableSecuritiesCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E56" s="25" t="inlineStr">
+      <c r="E57" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F56" s="26" t="inlineStr">
+      <c r="F57" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="25" t="n">
+    <row r="58">
+      <c r="B58" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C58" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D57" s="25" t="inlineStr">
+      <c r="D58" s="30" t="inlineStr">
         <is>
           <t>us-gaap:MarketableSecuritiesCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="E58" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F57" s="26" t="inlineStr">
+      <c r="F58" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="25" t="n">
+    <row r="59">
+      <c r="B59" s="30" t="n">
         <v>51</v>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C59" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D58" s="25" t="inlineStr">
+      <c r="D59" s="30" t="inlineStr">
         <is>
           <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E58" s="25" t="inlineStr">
+      <c r="E59" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F58" s="26" t="inlineStr">
+      <c r="F59" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="25" t="n">
+    <row r="60">
+      <c r="B60" s="30" t="n">
         <v>52</v>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C60" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D59" s="25" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="E60" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F59" s="26" t="inlineStr">
+      <c r="F60" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="25" t="n">
+    <row r="61">
+      <c r="B61" s="30" t="n">
         <v>53</v>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D60" s="25" t="inlineStr">
+      <c r="D61" s="30" t="inlineStr">
         <is>
           <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E60" s="25" t="inlineStr">
+      <c r="E61" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F60" s="26" t="inlineStr">
+      <c r="F61" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="25" t="n">
+    <row r="62">
+      <c r="B62" s="30" t="n">
         <v>54</v>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C62" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D61" s="25" t="inlineStr">
+      <c r="D62" s="30" t="inlineStr">
         <is>
           <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="E62" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F61" s="26" t="inlineStr">
+      <c r="F62" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="25" t="n">
+    <row r="63">
+      <c r="B63" s="30" t="n">
         <v>55</v>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C63" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D62" s="25" t="inlineStr">
+      <c r="D63" s="30" t="inlineStr">
         <is>
           <t>us-gaap:DebtInstrumentCarryingAmount · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E62" s="25" t="inlineStr">
+      <c r="E63" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F62" s="26" t="inlineStr">
+      <c r="F63" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="25" t="n">
+    <row r="64">
+      <c r="B64" s="30" t="n">
         <v>56</v>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D63" s="25" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebtCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F63" s="26" t="inlineStr">
+      <c r="F64" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="25" t="n">
+    <row r="65">
+      <c r="B65" s="30" t="n">
         <v>57</v>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D64" s="25" t="inlineStr">
+      <c r="D65" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebtCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E64" s="25" t="inlineStr">
+      <c r="E65" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F64" s="26" t="inlineStr">
+      <c r="F65" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="25" t="n">
+    <row r="66">
+      <c r="B66" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D65" s="25" t="inlineStr">
+      <c r="D66" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebtCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="E66" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F65" s="26" t="inlineStr">
+      <c r="F66" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="25" t="n">
+    <row r="67">
+      <c r="B67" s="30" t="n">
         <v>59</v>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C67" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D66" s="25" t="inlineStr">
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebtCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E66" s="25" t="inlineStr">
+      <c r="E67" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F66" s="26" t="inlineStr">
+      <c r="F67" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="25" t="n">
+    <row r="68">
+      <c r="B68" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C68" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D67" s="25" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LongTermDebtCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E67" s="25" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F67" s="26" t="inlineStr">
+      <c r="F68" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="25" t="n">
+    <row r="69">
+      <c r="B69" s="30" t="n">
         <v>61</v>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D68" s="25" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>us-gaap:StockholdersEquity · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E68" s="25" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F68" s="26" t="inlineStr">
+      <c r="F69" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="25" t="n">
+    <row r="70">
+      <c r="B70" s="30" t="n">
         <v>62</v>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D69" s="25" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>us-gaap:StockholdersEquity · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E69" s="25" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F69" s="26" t="inlineStr">
+      <c r="F70" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="25" t="n">
+    <row r="71">
+      <c r="B71" s="30" t="n">
         <v>63</v>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D70" s="25" t="inlineStr">
+      <c r="D71" s="30" t="inlineStr">
         <is>
           <t>us-gaap:StockholdersEquity · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E70" s="25" t="inlineStr">
+      <c r="E71" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F70" s="26" t="inlineStr">
+      <c r="F71" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="25" t="n">
+    <row r="72">
+      <c r="B72" s="30" t="n">
         <v>64</v>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C72" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D71" s="25" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>us-gaap:StockholdersEquity · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E71" s="25" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F71" s="26" t="inlineStr">
+      <c r="F72" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="25" t="n">
+    <row r="73">
+      <c r="B73" s="30" t="n">
         <v>65</v>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D72" s="25" t="inlineStr">
+      <c r="D73" s="30" t="inlineStr">
         <is>
           <t>us-gaap:StockholdersEquity · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E72" s="25" t="inlineStr">
+      <c r="E73" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F72" s="26" t="inlineStr">
+      <c r="F73" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="25" t="n">
+    <row r="74">
+      <c r="B74" s="30" t="n">
         <v>66</v>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C74" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D73" s="25" t="inlineStr">
+      <c r="D74" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E73" s="25" t="inlineStr">
+      <c r="E74" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F73" s="26" t="inlineStr">
+      <c r="F74" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="25" t="n">
+    <row r="75">
+      <c r="B75" s="30" t="n">
         <v>67</v>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C75" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D74" s="25" t="inlineStr">
+      <c r="D75" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E74" s="25" t="inlineStr">
+      <c r="E75" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F74" s="26" t="inlineStr">
+      <c r="F75" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="25" t="n">
+    <row r="76">
+      <c r="B76" s="30" t="n">
         <v>68</v>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C76" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D75" s="25" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E75" s="25" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F75" s="26" t="inlineStr">
+      <c r="F76" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="25" t="n">
+    <row r="77">
+      <c r="B77" s="30" t="n">
         <v>69</v>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C77" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D76" s="25" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E76" s="25" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F76" s="26" t="inlineStr">
+      <c r="F77" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="25" t="n">
+    <row r="78">
+      <c r="B78" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C78" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D77" s="25" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>us-gaap:CostOfGoodsAndServicesSold · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E77" s="25" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F77" s="26" t="inlineStr">
+      <c r="F78" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="25" t="n">
+    <row r="79">
+      <c r="B79" s="30" t="n">
         <v>71</v>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C79" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D78" s="25" t="inlineStr">
+      <c r="D79" s="30" t="inlineStr">
         <is>
           <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E78" s="25" t="inlineStr">
+      <c r="E79" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F78" s="26" t="inlineStr">
+      <c r="F79" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="25" t="n">
+    <row r="80">
+      <c r="B80" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C80" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D79" s="25" t="inlineStr">
+      <c r="D80" s="30" t="inlineStr">
         <is>
           <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E79" s="25" t="inlineStr">
+      <c r="E80" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F79" s="26" t="inlineStr">
+      <c r="F80" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="25" t="n">
+    <row r="81">
+      <c r="B81" s="30" t="n">
         <v>73</v>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C81" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D80" s="25" t="inlineStr">
+      <c r="D81" s="30" t="inlineStr">
         <is>
           <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E80" s="25" t="inlineStr">
+      <c r="E81" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F80" s="26" t="inlineStr">
+      <c r="F81" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="25" t="n">
+    <row r="82">
+      <c r="B82" s="30" t="n">
         <v>74</v>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C82" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D81" s="25" t="inlineStr">
+      <c r="D82" s="30" t="inlineStr">
         <is>
           <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E81" s="25" t="inlineStr">
+      <c r="E82" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F81" s="26" t="inlineStr">
+      <c r="F82" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="25" t="n">
+    <row r="83">
+      <c r="B83" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C83" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D82" s="25" t="inlineStr">
+      <c r="D83" s="30" t="inlineStr">
         <is>
           <t>us-gaap:ResearchAndDevelopmentExpense · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E82" s="25" t="inlineStr">
+      <c r="E83" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F82" s="26" t="inlineStr">
+      <c r="F83" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="25" t="n">
+    <row r="84">
+      <c r="B84" s="30" t="n">
         <v>76</v>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C84" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D83" s="25" t="inlineStr">
+      <c r="D84" s="30" t="inlineStr">
         <is>
           <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E83" s="25" t="inlineStr">
+      <c r="E84" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F83" s="26" t="inlineStr">
+      <c r="F84" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="25" t="n">
+    <row r="85">
+      <c r="B85" s="30" t="n">
         <v>77</v>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C85" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D84" s="25" t="inlineStr">
+      <c r="D85" s="30" t="inlineStr">
         <is>
           <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E84" s="25" t="inlineStr">
+      <c r="E85" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F84" s="26" t="inlineStr">
+      <c r="F85" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="25" t="n">
+    <row r="86">
+      <c r="B86" s="30" t="n">
         <v>78</v>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C86" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D85" s="25" t="inlineStr">
+      <c r="D86" s="30" t="inlineStr">
         <is>
           <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E85" s="25" t="inlineStr">
+      <c r="E86" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F85" s="26" t="inlineStr">
+      <c r="F86" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="25" t="n">
+    <row r="87">
+      <c r="B87" s="30" t="n">
         <v>79</v>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C87" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D86" s="25" t="inlineStr">
+      <c r="D87" s="30" t="inlineStr">
         <is>
           <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E86" s="25" t="inlineStr">
+      <c r="E87" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F86" s="26" t="inlineStr">
+      <c r="F87" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="25" t="n">
+    <row r="88">
+      <c r="B88" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C88" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D87" s="25" t="inlineStr">
+      <c r="D88" s="30" t="inlineStr">
         <is>
           <t>us-gaap:SellingGeneralAndAdministrativeExpense · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E87" s="25" t="inlineStr">
+      <c r="E88" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F87" s="26" t="inlineStr">
+      <c r="F88" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="25" t="n">
+    <row r="89">
+      <c r="B89" s="30" t="n">
         <v>81</v>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C89" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D88" s="25" t="inlineStr">
+      <c r="D89" s="30" t="inlineStr">
         <is>
           <t>us-gaap:InterestExpense · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E88" s="25" t="inlineStr">
+      <c r="E89" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F88" s="26" t="inlineStr">
+      <c r="F89" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="25" t="n">
+    <row r="90">
+      <c r="B90" s="30" t="n">
         <v>82</v>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C90" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D89" s="25" t="inlineStr">
+      <c r="D90" s="30" t="inlineStr">
         <is>
           <t>us-gaap:InterestExpense · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E89" s="25" t="inlineStr">
+      <c r="E90" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F89" s="26" t="inlineStr">
+      <c r="F90" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="25" t="n">
+    <row r="91">
+      <c r="B91" s="30" t="n">
         <v>83</v>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C91" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D90" s="25" t="inlineStr">
+      <c r="D91" s="30" t="inlineStr">
         <is>
           <t>us-gaap:InterestExpense · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E90" s="25" t="inlineStr">
+      <c r="E91" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F90" s="26" t="inlineStr">
+      <c r="F91" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="25" t="n">
+    <row r="92">
+      <c r="B92" s="30" t="n">
         <v>84</v>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C92" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D91" s="25" t="inlineStr">
+      <c r="D92" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E91" s="25" t="inlineStr">
+      <c r="E92" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F91" s="26" t="inlineStr">
+      <c r="F92" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="25" t="n">
+    <row r="93">
+      <c r="B93" s="30" t="n">
         <v>85</v>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C93" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D92" s="25" t="inlineStr">
+      <c r="D93" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E92" s="25" t="inlineStr">
+      <c r="E93" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F92" s="26" t="inlineStr">
+      <c r="F93" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="25" t="n">
+    <row r="94">
+      <c r="B94" s="30" t="n">
         <v>86</v>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C94" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D93" s="25" t="inlineStr">
+      <c r="D94" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E93" s="25" t="inlineStr">
+      <c r="E94" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F93" s="26" t="inlineStr">
+      <c r="F94" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="25" t="n">
+    <row r="95">
+      <c r="B95" s="30" t="n">
         <v>87</v>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C95" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D94" s="25" t="inlineStr">
+      <c r="D95" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E94" s="25" t="inlineStr">
+      <c r="E95" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F94" s="26" t="inlineStr">
+      <c r="F95" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="25" t="n">
+    <row r="96">
+      <c r="B96" s="30" t="n">
         <v>88</v>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C96" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D95" s="25" t="inlineStr">
+      <c r="D96" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeLossFromContinuingOperationsBeforeIncomeTaxesExtraordinaryItemsNoncontrollingInterest · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E95" s="25" t="inlineStr">
+      <c r="E96" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F95" s="26" t="inlineStr">
+      <c r="F96" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="25" t="n">
+    <row r="97">
+      <c r="B97" s="30" t="n">
         <v>89</v>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C97" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D96" s="25" t="inlineStr">
+      <c r="D97" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E96" s="25" t="inlineStr">
+      <c r="E97" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F96" s="26" t="inlineStr">
+      <c r="F97" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" s="25" t="n">
+    <row r="98">
+      <c r="B98" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="C98" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D97" s="25" t="inlineStr">
+      <c r="D98" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E97" s="25" t="inlineStr">
+      <c r="E98" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F97" s="26" t="inlineStr">
+      <c r="F98" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="25" t="n">
+    <row r="99">
+      <c r="B99" s="30" t="n">
         <v>91</v>
       </c>
-      <c r="C98" s="9" t="inlineStr">
+      <c r="C99" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D98" s="25" t="inlineStr">
+      <c r="D99" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E98" s="25" t="inlineStr">
+      <c r="E99" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F98" s="26" t="inlineStr">
+      <c r="F99" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" s="25" t="n">
+    <row r="100">
+      <c r="B100" s="30" t="n">
         <v>92</v>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C100" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D99" s="25" t="inlineStr">
+      <c r="D100" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E99" s="25" t="inlineStr">
+      <c r="E100" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F99" s="26" t="inlineStr">
+      <c r="F100" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="25" t="n">
+    <row r="101">
+      <c r="B101" s="30" t="n">
         <v>93</v>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C101" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D100" s="25" t="inlineStr">
+      <c r="D101" s="30" t="inlineStr">
         <is>
           <t>us-gaap:IncomeTaxExpenseBenefit · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E100" s="25" t="inlineStr">
+      <c r="E101" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F100" s="26" t="inlineStr">
+      <c r="F101" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="25" t="n">
+    <row r="102">
+      <c r="B102" s="30" t="n">
         <v>94</v>
       </c>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="C102" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D101" s="25" t="inlineStr">
+      <c r="D102" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsReceivableNetCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E101" s="25" t="inlineStr">
+      <c r="E102" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F101" s="26" t="inlineStr">
+      <c r="F102" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" s="25" t="n">
+    <row r="103">
+      <c r="B103" s="30" t="n">
         <v>95</v>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C103" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D102" s="25" t="inlineStr">
+      <c r="D103" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsReceivableNetCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E102" s="25" t="inlineStr">
+      <c r="E103" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F102" s="26" t="inlineStr">
+      <c r="F103" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" s="25" t="n">
+    <row r="104">
+      <c r="B104" s="30" t="n">
         <v>96</v>
       </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="C104" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D103" s="25" t="inlineStr">
+      <c r="D104" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsReceivableNetCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E103" s="25" t="inlineStr">
+      <c r="E104" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F103" s="26" t="inlineStr">
+      <c r="F104" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" s="25" t="n">
+    <row r="105">
+      <c r="B105" s="30" t="n">
         <v>97</v>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C105" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D104" s="25" t="inlineStr">
+      <c r="D105" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsReceivableNetCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E104" s="25" t="inlineStr">
+      <c r="E105" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F104" s="26" t="inlineStr">
+      <c r="F105" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" s="25" t="n">
+    <row r="106">
+      <c r="B106" s="30" t="n">
         <v>98</v>
       </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="C106" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D105" s="25" t="inlineStr">
+      <c r="D106" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsReceivableNetCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E105" s="25" t="inlineStr">
+      <c r="E106" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F105" s="26" t="inlineStr">
+      <c r="F106" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="B106" s="25" t="n">
+    <row r="107">
+      <c r="B107" s="30" t="n">
         <v>99</v>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C107" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D106" s="25" t="inlineStr">
+      <c r="D107" s="30" t="inlineStr">
         <is>
           <t>us-gaap:InventoryNet · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E106" s="25" t="inlineStr">
+      <c r="E107" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F106" s="26" t="inlineStr">
+      <c r="F107" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" s="25" t="n">
+    <row r="108">
+      <c r="B108" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C108" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D107" s="25" t="inlineStr">
+      <c r="D108" s="30" t="inlineStr">
         <is>
           <t>us-gaap:InventoryNet · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E107" s="25" t="inlineStr">
+      <c r="E108" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F107" s="26" t="inlineStr">
+      <c r="F108" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="25" t="n">
+    <row r="109">
+      <c r="B109" s="30" t="n">
         <v>101</v>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C109" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D108" s="25" t="inlineStr">
+      <c r="D109" s="30" t="inlineStr">
         <is>
           <t>us-gaap:InventoryNet · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E108" s="25" t="inlineStr">
+      <c r="E109" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F108" s="26" t="inlineStr">
+      <c r="F109" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" s="25" t="n">
+    <row r="110">
+      <c r="B110" s="30" t="n">
         <v>102</v>
       </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="C110" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D109" s="25" t="inlineStr">
+      <c r="D110" s="30" t="inlineStr">
         <is>
           <t>us-gaap:InventoryNet · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E109" s="25" t="inlineStr">
+      <c r="E110" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F109" s="26" t="inlineStr">
+      <c r="F110" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" s="25" t="n">
+    <row r="111">
+      <c r="B111" s="30" t="n">
         <v>103</v>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C111" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D110" s="25" t="inlineStr">
+      <c r="D111" s="30" t="inlineStr">
         <is>
           <t>us-gaap:InventoryNet · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E110" s="25" t="inlineStr">
+      <c r="E111" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F110" s="26" t="inlineStr">
+      <c r="F111" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="B111" s="25" t="n">
+    <row r="112">
+      <c r="B112" s="30" t="n">
         <v>104</v>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C112" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D111" s="25" t="inlineStr">
+      <c r="D112" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AssetsCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E111" s="25" t="inlineStr">
+      <c r="E112" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F111" s="26" t="inlineStr">
+      <c r="F112" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="B112" s="25" t="n">
+    <row r="113">
+      <c r="B113" s="30" t="n">
         <v>105</v>
       </c>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="C113" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D112" s="25" t="inlineStr">
+      <c r="D113" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AssetsCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E112" s="25" t="inlineStr">
+      <c r="E113" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F112" s="26" t="inlineStr">
+      <c r="F113" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" s="25" t="n">
+    <row r="114">
+      <c r="B114" s="30" t="n">
         <v>106</v>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C114" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D113" s="25" t="inlineStr">
+      <c r="D114" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AssetsCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E113" s="25" t="inlineStr">
+      <c r="E114" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F113" s="26" t="inlineStr">
+      <c r="F114" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="B114" s="25" t="n">
+    <row r="115">
+      <c r="B115" s="30" t="n">
         <v>107</v>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C115" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D114" s="25" t="inlineStr">
+      <c r="D115" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AssetsCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E114" s="25" t="inlineStr">
+      <c r="E115" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F114" s="26" t="inlineStr">
+      <c r="F115" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="B115" s="25" t="n">
+    <row r="116">
+      <c r="B116" s="30" t="n">
         <v>108</v>
       </c>
-      <c r="C115" s="9" t="inlineStr">
+      <c r="C116" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D115" s="25" t="inlineStr">
+      <c r="D116" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AssetsCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E115" s="25" t="inlineStr">
+      <c r="E116" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F115" s="26" t="inlineStr">
+      <c r="F116" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="B116" s="25" t="n">
+    <row r="117">
+      <c r="B117" s="30" t="n">
         <v>109</v>
       </c>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="C117" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D116" s="25" t="inlineStr">
+      <c r="D117" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E116" s="25" t="inlineStr">
+      <c r="E117" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F116" s="26" t="inlineStr">
+      <c r="F117" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="B117" s="25" t="n">
+    <row r="118">
+      <c r="B118" s="30" t="n">
         <v>110</v>
       </c>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="C118" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D117" s="25" t="inlineStr">
+      <c r="D118" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E117" s="25" t="inlineStr">
+      <c r="E118" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F117" s="26" t="inlineStr">
+      <c r="F118" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="B118" s="25" t="n">
+    <row r="119">
+      <c r="B119" s="30" t="n">
         <v>111</v>
       </c>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="C119" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D118" s="25" t="inlineStr">
+      <c r="D119" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E118" s="25" t="inlineStr">
+      <c r="E119" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F118" s="26" t="inlineStr">
+      <c r="F119" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="B119" s="25" t="n">
+    <row r="120">
+      <c r="B120" s="30" t="n">
         <v>112</v>
       </c>
-      <c r="C119" s="9" t="inlineStr">
+      <c r="C120" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D119" s="25" t="inlineStr">
+      <c r="D120" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E119" s="25" t="inlineStr">
+      <c r="E120" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F119" s="26" t="inlineStr">
+      <c r="F120" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" s="25" t="n">
+    <row r="121">
+      <c r="B121" s="30" t="n">
         <v>113</v>
       </c>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="C121" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D120" s="25" t="inlineStr">
+      <c r="D121" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PropertyPlantAndEquipmentNet · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E120" s="25" t="inlineStr">
+      <c r="E121" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F120" s="26" t="inlineStr">
+      <c r="F121" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="B121" s="25" t="n">
+    <row r="122">
+      <c r="B122" s="30" t="n">
         <v>114</v>
       </c>
-      <c r="C121" s="9" t="inlineStr">
+      <c r="C122" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D121" s="25" t="inlineStr">
+      <c r="D122" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Assets · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E121" s="25" t="inlineStr">
+      <c r="E122" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F121" s="26" t="inlineStr">
+      <c r="F122" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="B122" s="25" t="n">
+    <row r="123">
+      <c r="B123" s="30" t="n">
         <v>115</v>
       </c>
-      <c r="C122" s="9" t="inlineStr">
+      <c r="C123" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D122" s="25" t="inlineStr">
+      <c r="D123" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Assets · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E122" s="25" t="inlineStr">
+      <c r="E123" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F122" s="26" t="inlineStr">
+      <c r="F123" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="B123" s="25" t="n">
+    <row r="124">
+      <c r="B124" s="30" t="n">
         <v>116</v>
       </c>
-      <c r="C123" s="9" t="inlineStr">
+      <c r="C124" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D123" s="25" t="inlineStr">
+      <c r="D124" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Assets · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E123" s="25" t="inlineStr">
+      <c r="E124" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F123" s="26" t="inlineStr">
+      <c r="F124" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="B124" s="25" t="n">
+    <row r="125">
+      <c r="B125" s="30" t="n">
         <v>117</v>
       </c>
-      <c r="C124" s="9" t="inlineStr">
+      <c r="C125" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D124" s="25" t="inlineStr">
+      <c r="D125" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Assets · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E124" s="25" t="inlineStr">
+      <c r="E125" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F124" s="26" t="inlineStr">
+      <c r="F125" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="B125" s="25" t="n">
+    <row r="126">
+      <c r="B126" s="30" t="n">
         <v>118</v>
       </c>
-      <c r="C125" s="9" t="inlineStr">
+      <c r="C126" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D125" s="25" t="inlineStr">
+      <c r="D126" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Assets · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E125" s="25" t="inlineStr">
+      <c r="E126" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F125" s="26" t="inlineStr">
+      <c r="F126" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="B126" s="25" t="n">
+    <row r="127">
+      <c r="B127" s="30" t="n">
         <v>119</v>
       </c>
-      <c r="C126" s="9" t="inlineStr">
+      <c r="C127" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D126" s="25" t="inlineStr">
+      <c r="D127" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsPayableCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E126" s="25" t="inlineStr">
+      <c r="E127" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F126" s="26" t="inlineStr">
+      <c r="F127" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="B127" s="25" t="n">
+    <row r="128">
+      <c r="B128" s="30" t="n">
         <v>120</v>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C128" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D127" s="25" t="inlineStr">
+      <c r="D128" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsPayableCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E127" s="25" t="inlineStr">
+      <c r="E128" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F127" s="26" t="inlineStr">
+      <c r="F128" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="B128" s="25" t="n">
+    <row r="129">
+      <c r="B129" s="30" t="n">
         <v>121</v>
       </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="C129" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D128" s="25" t="inlineStr">
+      <c r="D129" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsPayableCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E128" s="25" t="inlineStr">
+      <c r="E129" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F128" s="26" t="inlineStr">
+      <c r="F129" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="B129" s="25" t="n">
+    <row r="130">
+      <c r="B130" s="30" t="n">
         <v>122</v>
       </c>
-      <c r="C129" s="9" t="inlineStr">
+      <c r="C130" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D129" s="25" t="inlineStr">
+      <c r="D130" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsPayableCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E129" s="25" t="inlineStr">
+      <c r="E130" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F129" s="26" t="inlineStr">
+      <c r="F130" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="B130" s="25" t="n">
+    <row r="131">
+      <c r="B131" s="30" t="n">
         <v>123</v>
       </c>
-      <c r="C130" s="9" t="inlineStr">
+      <c r="C131" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D130" s="25" t="inlineStr">
+      <c r="D131" s="30" t="inlineStr">
         <is>
           <t>us-gaap:AccountsPayableCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E130" s="25" t="inlineStr">
+      <c r="E131" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F130" s="26" t="inlineStr">
+      <c r="F131" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="B131" s="25" t="n">
+    <row r="132">
+      <c r="B132" s="30" t="n">
         <v>124</v>
       </c>
-      <c r="C131" s="9" t="inlineStr">
+      <c r="C132" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D131" s="25" t="inlineStr">
+      <c r="D132" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesCurrent · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E131" s="25" t="inlineStr">
+      <c r="E132" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F131" s="26" t="inlineStr">
+      <c r="F132" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="B132" s="25" t="n">
+    <row r="133">
+      <c r="B133" s="30" t="n">
         <v>125</v>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C133" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D132" s="25" t="inlineStr">
+      <c r="D133" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesCurrent · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E132" s="25" t="inlineStr">
+      <c r="E133" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F132" s="26" t="inlineStr">
+      <c r="F133" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="B133" s="25" t="n">
+    <row r="134">
+      <c r="B134" s="30" t="n">
         <v>126</v>
       </c>
-      <c r="C133" s="9" t="inlineStr">
+      <c r="C134" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D133" s="25" t="inlineStr">
+      <c r="D134" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesCurrent · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E133" s="25" t="inlineStr">
+      <c r="E134" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F133" s="26" t="inlineStr">
+      <c r="F134" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="B134" s="25" t="n">
+    <row r="135">
+      <c r="B135" s="30" t="n">
         <v>127</v>
       </c>
-      <c r="C134" s="9" t="inlineStr">
+      <c r="C135" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D134" s="25" t="inlineStr">
+      <c r="D135" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesCurrent · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E134" s="25" t="inlineStr">
+      <c r="E135" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F134" s="26" t="inlineStr">
+      <c r="F135" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="B135" s="25" t="n">
+    <row r="136">
+      <c r="B136" s="30" t="n">
         <v>128</v>
       </c>
-      <c r="C135" s="9" t="inlineStr">
+      <c r="C136" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D135" s="25" t="inlineStr">
+      <c r="D136" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesCurrent · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E135" s="25" t="inlineStr">
+      <c r="E136" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F135" s="26" t="inlineStr">
+      <c r="F136" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="B136" s="25" t="n">
+    <row r="137">
+      <c r="B137" s="30" t="n">
         <v>129</v>
       </c>
-      <c r="C136" s="9" t="inlineStr">
+      <c r="C137" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D136" s="25" t="inlineStr">
+      <c r="D137" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Liabilities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E136" s="25" t="inlineStr">
+      <c r="E137" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F136" s="26" t="inlineStr">
+      <c r="F137" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="B137" s="25" t="n">
+    <row r="138">
+      <c r="B138" s="30" t="n">
         <v>130</v>
       </c>
-      <c r="C137" s="9" t="inlineStr">
+      <c r="C138" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D137" s="25" t="inlineStr">
+      <c r="D138" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Liabilities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E137" s="25" t="inlineStr">
+      <c r="E138" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F137" s="26" t="inlineStr">
+      <c r="F138" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="B138" s="25" t="n">
+    <row r="139">
+      <c r="B139" s="30" t="n">
         <v>131</v>
       </c>
-      <c r="C138" s="9" t="inlineStr">
+      <c r="C139" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D138" s="25" t="inlineStr">
+      <c r="D139" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Liabilities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E138" s="25" t="inlineStr">
+      <c r="E139" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F138" s="26" t="inlineStr">
+      <c r="F139" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="B139" s="25" t="n">
+    <row r="140">
+      <c r="B140" s="30" t="n">
         <v>132</v>
       </c>
-      <c r="C139" s="9" t="inlineStr">
+      <c r="C140" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D139" s="25" t="inlineStr">
+      <c r="D140" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Liabilities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E139" s="25" t="inlineStr">
+      <c r="E140" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F139" s="26" t="inlineStr">
+      <c r="F140" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="B140" s="25" t="n">
+    <row r="141">
+      <c r="B141" s="30" t="n">
         <v>133</v>
       </c>
-      <c r="C140" s="9" t="inlineStr">
+      <c r="C141" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D140" s="25" t="inlineStr">
+      <c r="D141" s="30" t="inlineStr">
         <is>
           <t>us-gaap:Liabilities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E140" s="25" t="inlineStr">
+      <c r="E141" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F140" s="26" t="inlineStr">
+      <c r="F141" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="B141" s="25" t="n">
+    <row r="142">
+      <c r="B142" s="30" t="n">
         <v>134</v>
       </c>
-      <c r="C141" s="9" t="inlineStr">
+      <c r="C142" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D141" s="25" t="inlineStr">
+      <c r="D142" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E141" s="25" t="inlineStr">
+      <c r="E142" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F141" s="26" t="inlineStr">
+      <c r="F142" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="B142" s="25" t="n">
+    <row r="143">
+      <c r="B143" s="30" t="n">
         <v>135</v>
       </c>
-      <c r="C142" s="9" t="inlineStr">
+      <c r="C143" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D142" s="25" t="inlineStr">
+      <c r="D143" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E142" s="25" t="inlineStr">
+      <c r="E143" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F142" s="26" t="inlineStr">
+      <c r="F143" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="B143" s="25" t="n">
+    <row r="144">
+      <c r="B144" s="30" t="n">
         <v>136</v>
       </c>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="C144" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D143" s="25" t="inlineStr">
+      <c r="D144" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E143" s="25" t="inlineStr">
+      <c r="E144" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F143" s="26" t="inlineStr">
+      <c r="F144" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="B144" s="25" t="n">
+    <row r="145">
+      <c r="B145" s="30" t="n">
         <v>137</v>
       </c>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="C145" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D144" s="25" t="inlineStr">
+      <c r="D145" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E144" s="25" t="inlineStr">
+      <c r="E145" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F144" s="26" t="inlineStr">
+      <c r="F145" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="B145" s="25" t="n">
+    <row r="146">
+      <c r="B146" s="30" t="n">
         <v>138</v>
       </c>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="C146" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D145" s="25" t="inlineStr">
+      <c r="D146" s="30" t="inlineStr">
         <is>
           <t>us-gaap:LiabilitiesAndStockholdersEquity · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E145" s="25" t="inlineStr">
+      <c r="E146" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F145" s="26" t="inlineStr">
+      <c r="F146" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="B146" s="25" t="n">
+    <row r="147">
+      <c r="B147" s="30" t="n">
         <v>139</v>
       </c>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="C147" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D146" s="25" t="inlineStr">
+      <c r="D147" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E146" s="25" t="inlineStr">
+      <c r="E147" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F146" s="26" t="inlineStr">
+      <c r="F147" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="B147" s="25" t="n">
+    <row r="148">
+      <c r="B148" s="30" t="n">
         <v>140</v>
       </c>
-      <c r="C147" s="9" t="inlineStr">
+      <c r="C148" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D147" s="25" t="inlineStr">
+      <c r="D148" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E147" s="25" t="inlineStr">
+      <c r="E148" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F147" s="26" t="inlineStr">
+      <c r="F148" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="B148" s="25" t="n">
+    <row r="149">
+      <c r="B149" s="30" t="n">
         <v>141</v>
       </c>
-      <c r="C148" s="9" t="inlineStr">
+      <c r="C149" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D148" s="25" t="inlineStr">
+      <c r="D149" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E148" s="25" t="inlineStr">
+      <c r="E149" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F148" s="26" t="inlineStr">
+      <c r="F149" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="B149" s="25" t="n">
+    <row r="150">
+      <c r="B150" s="30" t="n">
         <v>142</v>
       </c>
-      <c r="C149" s="9" t="inlineStr">
+      <c r="C150" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D149" s="25" t="inlineStr">
+      <c r="D150" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E149" s="25" t="inlineStr">
+      <c r="E150" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F149" s="26" t="inlineStr">
+      <c r="F150" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="B150" s="25" t="n">
+    <row r="151">
+      <c r="B151" s="30" t="n">
         <v>143</v>
       </c>
-      <c r="C150" s="9" t="inlineStr">
+      <c r="C151" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D150" s="25" t="inlineStr">
+      <c r="D151" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInInvestingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E150" s="25" t="inlineStr">
+      <c r="E151" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F150" s="26" t="inlineStr">
+      <c r="F151" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="B151" s="25" t="n">
+    <row r="152">
+      <c r="B152" s="30" t="n">
         <v>144</v>
       </c>
-      <c r="C151" s="9" t="inlineStr">
+      <c r="C152" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D151" s="25" t="inlineStr">
+      <c r="D152" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E151" s="25" t="inlineStr">
+      <c r="E152" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F151" s="26" t="inlineStr">
+      <c r="F152" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="B152" s="25" t="n">
+    <row r="153">
+      <c r="B153" s="30" t="n">
         <v>145</v>
       </c>
-      <c r="C152" s="9" t="inlineStr">
+      <c r="C153" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D152" s="25" t="inlineStr">
+      <c r="D153" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E152" s="25" t="inlineStr">
+      <c r="E153" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F152" s="26" t="inlineStr">
+      <c r="F153" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="B153" s="25" t="n">
+    <row r="154">
+      <c r="B154" s="30" t="n">
         <v>146</v>
       </c>
-      <c r="C153" s="9" t="inlineStr">
+      <c r="C154" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D153" s="25" t="inlineStr">
+      <c r="D154" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E153" s="25" t="inlineStr">
+      <c r="E154" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F153" s="26" t="inlineStr">
+      <c r="F154" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="B154" s="25" t="n">
+    <row r="155">
+      <c r="B155" s="30" t="n">
         <v>147</v>
       </c>
-      <c r="C154" s="9" t="inlineStr">
+      <c r="C155" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D154" s="25" t="inlineStr">
+      <c r="D155" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E154" s="25" t="inlineStr">
+      <c r="E155" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F154" s="26" t="inlineStr">
+      <c r="F155" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="B155" s="25" t="n">
+    <row r="156">
+      <c r="B156" s="30" t="n">
         <v>148</v>
       </c>
-      <c r="C155" s="9" t="inlineStr">
+      <c r="C156" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D155" s="25" t="inlineStr">
+      <c r="D156" s="30" t="inlineStr">
         <is>
           <t>us-gaap:NetCashProvidedByUsedInFinancingActivities · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E155" s="25" t="inlineStr">
+      <c r="E156" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F155" s="26" t="inlineStr">
+      <c r="F156" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="B156" s="25" t="n">
+    <row r="157">
+      <c r="B157" s="30" t="n">
         <v>149</v>
       </c>
-      <c r="C156" s="9" t="inlineStr">
+      <c r="C157" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D156" s="25" t="inlineStr">
+      <c r="D157" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E156" s="25" t="inlineStr">
+      <c r="E157" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F156" s="26" t="inlineStr">
+      <c r="F157" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="B157" s="25" t="n">
+    <row r="158">
+      <c r="B158" s="30" t="n">
         <v>150</v>
       </c>
-      <c r="C157" s="9" t="inlineStr">
+      <c r="C158" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D157" s="25" t="inlineStr">
+      <c r="D158" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E157" s="25" t="inlineStr">
+      <c r="E158" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F157" s="26" t="inlineStr">
+      <c r="F158" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="B158" s="25" t="n">
+    <row r="159">
+      <c r="B159" s="30" t="n">
         <v>151</v>
       </c>
-      <c r="C158" s="9" t="inlineStr">
+      <c r="C159" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D158" s="25" t="inlineStr">
+      <c r="D159" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E158" s="25" t="inlineStr">
+      <c r="E159" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F158" s="26" t="inlineStr">
+      <c r="F159" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="B159" s="25" t="n">
+    <row r="160">
+      <c r="B160" s="30" t="n">
         <v>152</v>
       </c>
-      <c r="C159" s="9" t="inlineStr">
+      <c r="C160" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D159" s="25" t="inlineStr">
+      <c r="D160" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E159" s="25" t="inlineStr">
+      <c r="E160" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F159" s="26" t="inlineStr">
+      <c r="F160" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="B160" s="25" t="n">
+    <row r="161">
+      <c r="B161" s="30" t="n">
         <v>153</v>
       </c>
-      <c r="C160" s="9" t="inlineStr">
+      <c r="C161" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D160" s="25" t="inlineStr">
+      <c r="D161" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsForRepurchaseOfCommonStock · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E160" s="25" t="inlineStr">
+      <c r="E161" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F160" s="26" t="inlineStr">
+      <c r="F161" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="B161" s="25" t="n">
+    <row r="162">
+      <c r="B162" s="30" t="n">
         <v>154</v>
       </c>
-      <c r="C161" s="9" t="inlineStr">
+      <c r="C162" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2021 10-K</t>
         </is>
       </c>
-      <c r="D161" s="25" t="inlineStr">
+      <c r="D162" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsOfDividends · period ending 2021-09-25 · USD · filed 2021-10-29</t>
         </is>
       </c>
-      <c r="E161" s="25" t="inlineStr">
+      <c r="E162" s="30" t="inlineStr">
         <is>
           <t>0000320193-21-000105</t>
         </is>
       </c>
-      <c r="F161" s="26" t="inlineStr">
+      <c r="F162" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019321000105/0000320193-21-000105-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="B162" s="25" t="n">
+    <row r="163">
+      <c r="B163" s="30" t="n">
         <v>155</v>
       </c>
-      <c r="C162" s="9" t="inlineStr">
+      <c r="C163" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2022 10-K</t>
         </is>
       </c>
-      <c r="D162" s="25" t="inlineStr">
+      <c r="D163" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsOfDividends · period ending 2022-09-24 · USD · filed 2022-10-28</t>
         </is>
       </c>
-      <c r="E162" s="25" t="inlineStr">
+      <c r="E163" s="30" t="inlineStr">
         <is>
           <t>0000320193-22-000108</t>
         </is>
       </c>
-      <c r="F162" s="26" t="inlineStr">
+      <c r="F163" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019322000108/0000320193-22-000108-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="B163" s="25" t="n">
+    <row r="164">
+      <c r="B164" s="30" t="n">
         <v>156</v>
       </c>
-      <c r="C163" s="9" t="inlineStr">
+      <c r="C164" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2023 10-K</t>
         </is>
       </c>
-      <c r="D163" s="25" t="inlineStr">
+      <c r="D164" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsOfDividends · period ending 2023-09-30 · USD · filed 2023-11-03</t>
         </is>
       </c>
-      <c r="E163" s="25" t="inlineStr">
+      <c r="E164" s="30" t="inlineStr">
         <is>
           <t>0000320193-23-000106</t>
         </is>
       </c>
-      <c r="F163" s="26" t="inlineStr">
+      <c r="F164" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019323000106/0000320193-23-000106-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="B164" s="25" t="n">
+    <row r="165">
+      <c r="B165" s="30" t="n">
         <v>157</v>
       </c>
-      <c r="C164" s="9" t="inlineStr">
+      <c r="C165" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2024 10-K</t>
         </is>
       </c>
-      <c r="D164" s="25" t="inlineStr">
+      <c r="D165" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsOfDividends · period ending 2024-09-28 · USD · filed 2024-11-01</t>
         </is>
       </c>
-      <c r="E164" s="25" t="inlineStr">
+      <c r="E165" s="30" t="inlineStr">
         <is>
           <t>0000320193-24-000123</t>
         </is>
       </c>
-      <c r="F164" s="26" t="inlineStr">
+      <c r="F165" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019324000123/0000320193-24-000123-index.htm</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="B165" s="25" t="n">
+    <row r="166">
+      <c r="B166" s="30" t="n">
         <v>158</v>
       </c>
-      <c r="C165" s="9" t="inlineStr">
+      <c r="C166" s="15" t="inlineStr">
         <is>
           <t>AAPL FY2025 10-K</t>
         </is>
       </c>
-      <c r="D165" s="25" t="inlineStr">
+      <c r="D166" s="30" t="inlineStr">
         <is>
           <t>us-gaap:PaymentsOfDividends · period ending 2025-09-27 · USD · filed 2025-10-31</t>
         </is>
       </c>
-      <c r="E165" s="25" t="inlineStr">
+      <c r="E166" s="30" t="inlineStr">
         <is>
           <t>0000320193-25-000079</t>
         </is>
       </c>
-      <c r="F165" s="26" t="inlineStr">
+      <c r="F166" s="31" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/320193/000032019325000079/0000320193-25-000079-index.htm</t>
         </is>
@@ -6747,165 +7517,166 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId159"/>
 </worksheet>
 </file>
--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 24 August 2026 at 11:21 UTC</t>
+          <t>Generated 24 August 2026 at 19:54 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 24 August 2026 at 19:54 UTC</t>
+          <t>Generated 25 August 2026 at 08:57 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 August 2026 at 08:57 UTC</t>
+          <t>Generated 25 August 2026 at 09:00 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 August 2026 at 09:00 UTC</t>
+          <t>Generated 25 August 2026 at 09:17 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 August 2026 at 09:17 UTC</t>
+          <t>Generated 25 August 2026 at 09:19 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 August 2026 at 09:19 UTC</t>
+          <t>Generated 26 August 2026 at 07:28 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 26 August 2026 at 07:28 UTC</t>
+          <t>Generated 27 August 2026 at 17:52 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 27 August 2026 at 17:52 UTC</t>
+          <t>Generated 28 August 2026 at 09:21 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 09:21 UTC</t>
+          <t>Generated 28 August 2026 at 10:01 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 10:01 UTC</t>
+          <t>Generated 28 August 2026 at 10:29 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 10:29 UTC</t>
+          <t>Generated 28 August 2026 at 12:34 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 12:34 UTC</t>
+          <t>Generated 28 August 2026 at 12:41 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 12:41 UTC</t>
+          <t>Generated 28 August 2026 at 18:58 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 August 2026 at 18:58 UTC</t>
+          <t>Generated 29 August 2026 at 12:49 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 29 August 2026 at 12:49 UTC</t>
+          <t>Generated 29 August 2026 at 23:34 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 29 August 2026 at 23:34 UTC</t>
+          <t>Generated 30 August 2026 at 12:11 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 30 August 2026 at 12:11 UTC</t>
+          <t>Generated 31 August 2026 at 14:21 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 31 August 2026 at 14:21 UTC</t>
+          <t>Generated 01 September 2026 at 11:58 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 01 September 2026 at 11:58 UTC</t>
+          <t>Generated 02 September 2026 at 11:41 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 02 September 2026 at 11:41 UTC</t>
+          <t>Generated 03 September 2026 at 11:40 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 03 September 2026 at 11:40 UTC</t>
+          <t>Generated 04 September 2026 at 11:41 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 04 September 2026 at 11:41 UTC</t>
+          <t>Generated 05 September 2026 at 10:54 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 05 September 2026 at 10:54 UTC</t>
+          <t>Generated 06 September 2026 at 11:18 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 06 September 2026 at 11:18 UTC</t>
+          <t>Generated 07 September 2026 at 12:59 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 07 September 2026 at 12:59 UTC</t>
+          <t>Generated 08 September 2026 at 11:41 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 08 September 2026 at 11:41 UTC</t>
+          <t>Generated 09 September 2026 at 11:48 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 09 September 2026 at 11:48 UTC</t>
+          <t>Generated 10 September 2026 at 11:45 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 10 September 2026 at 11:45 UTC</t>
+          <t>Generated 11 September 2026 at 11:45 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/AAPL_company_profile.xlsx
+++ b/samples/AAPL_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 11 September 2026 at 11:45 UTC</t>
+          <t>Generated 12 September 2026 at 11:12 UTC</t>
         </is>
       </c>
     </row>
